--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -660,49 +660,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 138534억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 138537억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 145916억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146053억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152619억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152887억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 148198억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 148598억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 147754억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 148286억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146360억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146891억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 143805억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 144338억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 134797억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 135330억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -912,37 +912,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4640억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4641억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5058억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5059억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5566억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5568억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5994억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5998억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 6440억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 6445억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 6853억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 6859억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1749,49 +1749,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 138534억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 138537억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 145916억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146053억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152619억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152887억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 148198억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 148598억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 147754억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 148286억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146360억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146891억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 143805억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 144338억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 134797억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 135330억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2216,37 +2216,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4640억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4641억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5058억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5059억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5566억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5568억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5994억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5998억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 6440억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 6445억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 6853억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 6859억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6402,29 +6402,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.218375</v>
+        <v>0.218401</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.279902</v>
+        <v>0.281103</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.296138</v>
+        <v>0.298414</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.143218</v>
+        <v>0.146306</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.066555</v>
+        <v>0.070369</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.003041</v>
+        <v>0.005741</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.057754</v>
+        <v>-0.055918</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.09042500000000001</v>
+        <v>-0.08928899999999999</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6551,13 +6551,13 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.045776</v>
+        <v>0.045778</v>
       </c>
       <c r="AG22" s="24" t="n">
         <v>0.045776</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.045776</v>
+        <v>0.045777</v>
       </c>
       <c r="AI22" s="24" t="n">
         <v>0.045776</v>
@@ -6570,13 +6570,13 @@
         <v>0.045778</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.045777</v>
+        <v>0.045776</v>
       </c>
       <c r="AM22" s="24" t="n">
         <v>0.045776</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.045777</v>
+        <v>0.045776</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6706,10 +6706,10 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.088341</v>
+        <v>0.088339</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08834</v>
+        <v>0.088339</v>
       </c>
       <c r="AH23" s="24" t="n">
         <v>0.088339</v>
@@ -6722,16 +6722,16 @@
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088341</v>
+        <v>0.08834</v>
       </c>
       <c r="AL23" s="24" t="n">
         <v>0.088341</v>
       </c>
       <c r="AM23" s="24" t="n">
+        <v>0.088339</v>
+      </c>
+      <c r="AN23" s="24" t="n">
         <v>0.08834</v>
-      </c>
-      <c r="AN23" s="24" t="n">
-        <v>0.088341</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -6986,26 +6986,26 @@
         <v>41.36</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>45.56</v>
+        <v>45.57</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>54.65</v>
+        <v>54.67</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>58.85</v>
+        <v>58.89</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>63.23</v>
+        <v>63.28</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>67.29000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7445,32 +7445,32 @@
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.049989</v>
+        <v>0.049988</v>
       </c>
       <c r="AG28" s="24" t="n">
+        <v>0.049994</v>
+      </c>
+      <c r="AH28" s="24" t="n">
+        <v>0.049999</v>
+      </c>
+      <c r="AI28" s="24" t="n">
         <v>0.049992</v>
-      </c>
-      <c r="AH28" s="24" t="n">
-        <v>0.050009</v>
-      </c>
-      <c r="AI28" s="24" t="n">
-        <v>0.050003</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.050008</v>
+        <v>0.050003</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.049999</v>
+        <v>0.050006</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.049995</v>
+        <v>0.049993</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.050006</v>
+        <v>0.050005</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -7865,7 +7865,7 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH31" s="29" t="n">
         <v>0</v>
@@ -7875,16 +7875,16 @@
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AL31" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AM31" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AL31" s="29" t="n">
+      <c r="AN31" s="29" t="n">
         <v>-0</v>
-      </c>
-      <c r="AM31" s="29" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AN31" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>0</v>
@@ -8003,16 +8003,16 @@
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AL32" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AM32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AL32" s="29" t="n">
+      <c r="AN32" s="29" t="n">
         <v>-0</v>
-      </c>
-      <c r="AM32" s="29" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AN32" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8337,26 +8337,26 @@
         <v>0.101649</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.10169</v>
+        <v>0.101778</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.08998100000000001</v>
+        <v>0.090118</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.100408</v>
+        <v>0.100633</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.07696799999999999</v>
+        <v>0.077184</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.07442799999999999</v>
+        <v>0.074625</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.064083</v>
+        <v>0.06424299999999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.07047100000000001</v>
+        <v>0.07065299999999999</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8989,26 +8989,26 @@
         <v>0.284195</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>0.049663</v>
+        <v>0.049242</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>0.31982</v>
+        <v>0.319257</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.07457800000000001</v>
+        <v>-0.07581400000000001</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.173504</v>
+        <v>-0.175386</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.128308</v>
+        <v>-0.130365</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.069966</v>
+        <v>-0.072557</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.016028</v>
+        <v>-0.017833</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9121,13 +9121,13 @@
         <v>-0.189453</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.181443</v>
+        <v>-0.183505</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.173536</v>
+        <v>-0.175705</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.163218</v>
+        <v>-0.165517</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9409,10 +9409,10 @@
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.088341</v>
+        <v>0.088339</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.08834</v>
+        <v>0.088339</v>
       </c>
       <c r="AH44" s="24" t="n">
         <v>0.088339</v>
@@ -9425,16 +9425,16 @@
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.088341</v>
+        <v>0.08834</v>
       </c>
       <c r="AL44" s="24" t="n">
         <v>0.088341</v>
       </c>
       <c r="AM44" s="24" t="n">
+        <v>0.088339</v>
+      </c>
+      <c r="AN44" s="24" t="n">
         <v>0.08834</v>
-      </c>
-      <c r="AN44" s="24" t="n">
-        <v>0.088341</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -38334,7 +38334,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1880.5</v>
+        <v>1881.1</v>
       </c>
     </row>
     <row r="30">
@@ -38354,7 +38354,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.94</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="32">
@@ -38374,7 +38374,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2414</v>
+        <v>0.2415</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -21,9 +21,9 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$111</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$121</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
-    <definedName name="BS별도">BS별도!$C$5:$AO$110</definedName>
+    <definedName name="BS별도">BS별도!$C$5:$AO$120</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
     <definedName name="subQ">subQ!$A$5:$AO$40</definedName>
   </definedNames>
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146053억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146465억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152887억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154837억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 148598억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 153753억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 148286억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 158686억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146891억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 164367억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 144338억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 170116억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 135330억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 170098억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -888,61 +888,61 @@
     <comment ref="AC25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3071억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3071억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3389억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3389억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3823억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3823억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4212억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4212억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4641억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4642억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5059억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5065억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5568억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5590억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5998억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 6046억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 6445억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 6541억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 6859억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 7019억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1755,43 +1755,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146053억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146465억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152887억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154837억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 148598억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 153753억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 148286억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 158686억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146891억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 164367억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 144338억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 170116억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 135330억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 170098억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2192,61 +2192,61 @@
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3071억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3071억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3389억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3389억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3823억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3823억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4212억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4212억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4641억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4642억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5059억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5065억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5568억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5590억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5998억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 6046억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 6445억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 6541억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 6859억 × 3.93% − 총차입금 0억 × 3.56% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 7019억 × 3.93% − 총차입금 0억 × 3.01% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4219,7 +4219,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.7, "op_wape_pct": 44.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 3305.76, "rev_act": 2973.45, "op_pred": 199.62, "op_act": 266.31}, {"q": "2025Q4", "rev_pred": 4386.85, "rev_act": 3678.3, "op_pred": 264.9, "op_act": 473.48}, {"q": "2026Q1", "rev_pred": 3679.41, "rev_act": 3452.39, "op_pred": 222.19, "op_act": 513.79}, {"q": "2026Q2", "rev_pred": 3680.92, "rev_act": 3622.2, "op_pred": 222.28, "op_act": 379.11}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.7, "op_wape_pct": 44.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 13.3, "wape_trend": 12.7, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 3305.76, "rev_act": 2973.45, "op_pred": 199.62, "op_act": 266.31}, {"q": "2025Q4", "rev_pred": 4386.85, "rev_act": 3678.3, "op_pred": 264.9, "op_act": 473.48}, {"q": "2026Q1", "rev_pred": 3679.41, "rev_act": 3452.39, "op_pred": 222.19, "op_act": 513.79}, {"q": "2026Q2", "rev_pred": 3680.92, "rev_act": 3622.2, "op_pred": 222.28, "op_act": 379.11}]}</t>
         </is>
       </c>
     </row>
@@ -6405,26 +6405,26 @@
         <v>0.218401</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.281103</v>
+        <v>0.284722</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.298414</v>
+        <v>0.314979</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.146306</v>
+        <v>0.186077</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.070369</v>
+        <v>0.145438</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.005741</v>
+        <v>0.122221</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.055918</v>
+        <v>0.09866999999999999</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.08928899999999999</v>
+        <v>0.106303</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6567,16 +6567,16 @@
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.045778</v>
+        <v>0.045777</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.045776</v>
+        <v>0.045777</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.045776</v>
+        <v>0.045777</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.045776</v>
+        <v>0.045777</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6709,26 +6709,26 @@
         <v>0.088339</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.088339</v>
+        <v>0.08834</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088339</v>
+        <v>0.08834</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.088341</v>
+        <v>0.08834</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08834</v>
+        <v>0.088341</v>
       </c>
       <c r="AL23" s="24" t="n">
         <v>0.088341</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088339</v>
+        <v>0.08834</v>
       </c>
       <c r="AN23" s="24" t="n">
         <v>0.08834</v>
@@ -6986,26 +6986,26 @@
         <v>41.36</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>45.57</v>
+        <v>45.58</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>49.67</v>
+        <v>49.73</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>54.67</v>
+        <v>54.89</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>58.89</v>
+        <v>59.37</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>63.28</v>
+        <v>64.22</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>67.34999999999999</v>
+        <v>68.92</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7448,29 +7448,29 @@
         <v>0.049988</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.049994</v>
+        <v>0.049999</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.049999</v>
+        <v>0.049993</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.049992</v>
+        <v>0.049998</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.050003</v>
+        <v>0.049991</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.050006</v>
+        <v>0.049993</v>
       </c>
       <c r="AM28" s="24" t="n">
+        <v>0.050005</v>
+      </c>
+      <c r="AN28" s="24" t="n">
         <v>0.049993</v>
-      </c>
-      <c r="AN28" s="24" t="n">
-        <v>0.050005</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -7865,20 +7865,20 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM31" s="29" t="n">
         <v>0</v>
@@ -7993,20 +7993,20 @@
         <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
@@ -8337,26 +8337,26 @@
         <v>0.101649</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.101778</v>
+        <v>0.102039</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.090118</v>
+        <v>0.091129</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.100633</v>
+        <v>0.103692</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.077184</v>
+        <v>0.08165699999999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.074625</v>
+        <v>0.081805</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.06424299999999999</v>
+        <v>0.073104</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.07065299999999999</v>
+        <v>0.084656</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8989,26 +8989,26 @@
         <v>0.284195</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>0.049242</v>
+        <v>0.048822</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>0.319257</v>
+        <v>0.314189</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.07581400000000001</v>
+        <v>-0.087351</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.175386</v>
+        <v>-0.197215</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.130365</v>
+        <v>-0.173355</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.072557</v>
+        <v>-0.142245</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.017833</v>
+        <v>-0.126862</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9114,20 +9114,20 @@
         <v>-0.196864</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.194444</v>
+        <v>-0.196296</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.189453</v>
+        <v>-0.193359</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.183505</v>
+        <v>-0.189691</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.175705</v>
+        <v>-0.186551</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.165517</v>
+        <v>-0.184332</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9412,26 +9412,26 @@
         <v>0.088339</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.088339</v>
+        <v>0.08834</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.088339</v>
+        <v>0.08834</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.088341</v>
+        <v>0.08834</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.08834</v>
+        <v>0.088341</v>
       </c>
       <c r="AL44" s="24" t="n">
         <v>0.088341</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.088339</v>
+        <v>0.08834</v>
       </c>
       <c r="AN44" s="24" t="n">
         <v>0.08834</v>
@@ -9929,7 +9929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO111"/>
+  <dimension ref="A1:AO121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13378,13 +13378,13 @@
       <c r="P51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
       <c r="Y51" s="18" t="n">
-        <v>53008.75</v>
+        <v>96055.75</v>
       </c>
       <c r="Z51" s="34" t="n">
-        <v>53008.75</v>
+        <v>96055.75</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>55391.85</v>
+        <v>100793.85</v>
       </c>
       <c r="AB51" s="5" t="n"/>
       <c r="AC51" s="10" t="n"/>
@@ -13440,13 +13440,13 @@
       <c r="P52" s="9" t="n"/>
       <c r="U52" s="9" t="n"/>
       <c r="Y52" s="18" t="n">
-        <v>-357805.28</v>
+        <v>-314758.28</v>
       </c>
       <c r="Z52" s="34" t="n">
-        <v>-357805.28</v>
+        <v>-314758.28</v>
       </c>
       <c r="AA52" s="18" t="n">
-        <v>-65429.11</v>
+        <v>-20027.11</v>
       </c>
       <c r="AB52" s="5" t="n"/>
       <c r="AC52" s="10" t="n"/>
@@ -13633,7 +13633,15 @@
       </c>
       <c r="P56" s="9" t="n"/>
       <c r="U56" s="9" t="n"/>
-      <c r="Z56" s="9" t="n"/>
+      <c r="Y56" s="18" t="n">
+        <v>43047</v>
+      </c>
+      <c r="Z56" s="34" t="n">
+        <v>43047</v>
+      </c>
+      <c r="AA56" s="18" t="n">
+        <v>45402</v>
+      </c>
       <c r="AB56" s="5" t="n"/>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
@@ -15205,7 +15213,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="F91" s="9" t="n"/>
@@ -15213,8 +15221,11 @@
       <c r="P91" s="9" t="n"/>
       <c r="U91" s="9" t="n"/>
       <c r="Z91" s="9" t="n"/>
+      <c r="AA91" s="18" t="n">
+        <v>3273.17</v>
+      </c>
       <c r="AB91" s="19" t="n">
-        <v>0</v>
+        <v>1784.17</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -15236,42 +15247,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>-9581.959999999999</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="18" t="n">
-        <v>-1811.77</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>-14782.51</v>
-      </c>
-      <c r="I92" s="18" t="n">
-        <v>9343.35</v>
-      </c>
-      <c r="J92" s="18" t="n">
-        <v>-13861.77</v>
-      </c>
-      <c r="K92" s="34" t="n">
-        <v>-21112.7</v>
-      </c>
-      <c r="L92" s="18" t="n">
-        <v>19550.48</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>-29140.26</v>
-      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="P92" s="9" t="n"/>
       <c r="U92" s="9" t="n"/>
       <c r="Z92" s="9" t="n"/>
       <c r="AA92" s="18" t="n">
-        <v>48345.58</v>
+        <v>0</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>174502.68</v>
+        <v>0</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -15293,41 +15281,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>-9.16</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>-6.37</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>-72.43000000000001</v>
-      </c>
-      <c r="K93" s="34" t="n">
-        <v>-65.56</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>-45.8</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>-55.2</v>
-      </c>
+      <c r="K93" s="9" t="n"/>
       <c r="P93" s="9" t="n"/>
       <c r="U93" s="9" t="n"/>
       <c r="Z93" s="9" t="n"/>
       <c r="AA93" s="18" t="n">
-        <v>-1606.38</v>
-      </c>
-      <c r="AB93" s="5" t="n"/>
+        <v>552.4299999999999</v>
+      </c>
+      <c r="AB93" s="19" t="n">
+        <v>726.1</v>
+      </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
       <c r="AE93" s="11" t="n"/>
@@ -15348,42 +15315,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>-2787.46</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="G94" s="18" t="n">
-        <v>1473.28</v>
-      </c>
-      <c r="H94" s="18" t="n">
-        <v>-3699.09</v>
-      </c>
-      <c r="I94" s="18" t="n">
-        <v>-38914.88</v>
-      </c>
-      <c r="J94" s="18" t="n">
-        <v>-13368.48</v>
-      </c>
-      <c r="K94" s="34" t="n">
-        <v>-54509.17</v>
-      </c>
-      <c r="L94" s="18" t="n">
-        <v>-3086.88</v>
-      </c>
-      <c r="M94" s="18" t="n">
-        <v>-11699.19</v>
-      </c>
+      <c r="K94" s="9" t="n"/>
       <c r="P94" s="9" t="n"/>
       <c r="U94" s="9" t="n"/>
       <c r="Z94" s="9" t="n"/>
       <c r="AA94" s="18" t="n">
-        <v>-265353.43</v>
+        <v>66794.41</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>-34521.93</v>
+        <v>40928.65</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -15405,33 +15349,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>0</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F95" s="9" t="n"/>
-      <c r="I95" s="18" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="J95" s="18" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="K95" s="9" t="n"/>
-      <c r="L95" s="18" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="M95" s="18" t="n">
-        <v>15.92</v>
-      </c>
       <c r="P95" s="9" t="n"/>
       <c r="U95" s="9" t="n"/>
       <c r="Z95" s="9" t="n"/>
       <c r="AA95" s="18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB95" s="5" t="n"/>
+        <v>49388.18</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>32548.55</v>
+      </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
       <c r="AE95" s="11" t="n"/>
@@ -15452,18 +15383,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>178.02</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F96" s="9" t="n"/>
       <c r="K96" s="9" t="n"/>
       <c r="P96" s="9" t="n"/>
       <c r="U96" s="9" t="n"/>
       <c r="Z96" s="9" t="n"/>
-      <c r="AB96" s="5" t="n"/>
+      <c r="AA96" s="18" t="n">
+        <v>7836.39</v>
+      </c>
+      <c r="AB96" s="19" t="n">
+        <v>-4059.95</v>
+      </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
       <c r="AE96" s="11" t="n"/>
@@ -15484,41 +15417,20 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E97" s="18" t="n">
-        <v>2782.22</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F97" s="9" t="n"/>
-      <c r="G97" s="18" t="n">
-        <v>1716.49</v>
-      </c>
-      <c r="H97" s="18" t="n">
-        <v>1999.55</v>
-      </c>
-      <c r="I97" s="18" t="n">
-        <v>2897.04</v>
-      </c>
-      <c r="J97" s="18" t="n">
-        <v>2405.25</v>
-      </c>
-      <c r="K97" s="34" t="n">
-        <v>9018.33</v>
-      </c>
-      <c r="L97" s="18" t="n">
-        <v>4536.04</v>
-      </c>
-      <c r="M97" s="18" t="n">
-        <v>11065.58</v>
-      </c>
+      <c r="K97" s="9" t="n"/>
       <c r="P97" s="9" t="n"/>
       <c r="U97" s="9" t="n"/>
       <c r="Z97" s="9" t="n"/>
       <c r="AA97" s="18" t="n">
-        <v>23598.89</v>
-      </c>
-      <c r="AB97" s="5" t="n"/>
+        <v>2517.68</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>-2358.13</v>
+      </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
       <c r="AE97" s="11" t="n"/>
@@ -15539,41 +15451,20 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E98" s="18" t="n">
-        <v>2916.22</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F98" s="9" t="n"/>
-      <c r="G98" s="18" t="n">
-        <v>1730.49</v>
-      </c>
-      <c r="H98" s="18" t="n">
-        <v>2129.35</v>
-      </c>
-      <c r="I98" s="18" t="n">
-        <v>3194.89</v>
-      </c>
-      <c r="J98" s="18" t="n">
-        <v>2601.13</v>
-      </c>
-      <c r="K98" s="34" t="n">
-        <v>9655.860000000001</v>
-      </c>
-      <c r="L98" s="18" t="n">
-        <v>4539.04</v>
-      </c>
-      <c r="M98" s="18" t="n">
-        <v>11062.58</v>
-      </c>
+      <c r="K98" s="9" t="n"/>
       <c r="P98" s="9" t="n"/>
       <c r="U98" s="9" t="n"/>
       <c r="Z98" s="9" t="n"/>
       <c r="AA98" s="18" t="n">
-        <v>24939.45</v>
-      </c>
-      <c r="AB98" s="5" t="n"/>
+        <v>3123.64</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>838.03</v>
+      </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
       <c r="AE98" s="11" t="n"/>
@@ -15594,38 +15485,20 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E99" s="18" t="n">
-        <v>134</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F99" s="9" t="n"/>
-      <c r="G99" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="H99" s="18" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="I99" s="18" t="n">
-        <v>297.85</v>
-      </c>
-      <c r="J99" s="18" t="n">
-        <v>195.88</v>
-      </c>
-      <c r="K99" s="34" t="n">
-        <v>637.53</v>
-      </c>
-      <c r="L99" s="18" t="n">
-        <v>3</v>
-      </c>
+      <c r="K99" s="9" t="n"/>
       <c r="P99" s="9" t="n"/>
       <c r="U99" s="9" t="n"/>
       <c r="Z99" s="9" t="n"/>
       <c r="AA99" s="18" t="n">
-        <v>1340.56</v>
-      </c>
-      <c r="AB99" s="5" t="n"/>
+        <v>138535</v>
+      </c>
+      <c r="AB99" s="19" t="n">
+        <v>51104.13</v>
+      </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
       <c r="AE99" s="11" t="n"/>
@@ -15646,42 +15519,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E100" s="18" t="n">
-        <v>724.25</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F100" s="9" t="n"/>
-      <c r="G100" s="18" t="n">
-        <v>10235.29</v>
-      </c>
-      <c r="H100" s="18" t="n">
-        <v>8981.059999999999</v>
-      </c>
-      <c r="I100" s="18" t="n">
-        <v>65245.88</v>
-      </c>
-      <c r="J100" s="18" t="n">
-        <v>-7709.98</v>
-      </c>
-      <c r="K100" s="34" t="n">
-        <v>76752.25</v>
-      </c>
-      <c r="L100" s="18" t="n">
-        <v>-4502.75</v>
-      </c>
-      <c r="M100" s="18" t="n">
-        <v>7267.09</v>
-      </c>
+      <c r="K100" s="9" t="n"/>
       <c r="P100" s="9" t="n"/>
       <c r="U100" s="9" t="n"/>
       <c r="Z100" s="9" t="n"/>
       <c r="AA100" s="18" t="n">
-        <v>-968</v>
+        <v>2720.74</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>-43836.32</v>
+        <v>1058.07</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -15703,38 +15553,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E101" s="18" t="n">
-        <v>35000</v>
+          <t>(비지배주주지분)당기순이익</t>
+        </is>
       </c>
       <c r="F101" s="9" t="n"/>
-      <c r="G101" s="18" t="n">
-        <v>25000</v>
-      </c>
-      <c r="H101" s="18" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I101" s="18" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J101" s="18" t="n">
-        <v>16000</v>
-      </c>
-      <c r="K101" s="34" t="n">
-        <v>81000</v>
-      </c>
-      <c r="L101" s="18" t="n">
-        <v>31000</v>
-      </c>
-      <c r="M101" s="18" t="n">
-        <v>49000</v>
-      </c>
+      <c r="K101" s="9" t="n"/>
       <c r="P101" s="9" t="n"/>
       <c r="U101" s="9" t="n"/>
       <c r="Z101" s="9" t="n"/>
-      <c r="AB101" s="5" t="n"/>
+      <c r="AB101" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
       <c r="AE101" s="11" t="n"/>
@@ -15755,32 +15584,43 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E102" s="18" t="n">
-        <v>1082</v>
+        <v>-9581.959999999999</v>
       </c>
       <c r="F102" s="9" t="n"/>
       <c r="G102" s="18" t="n">
-        <v>686</v>
+        <v>-1811.77</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>473</v>
+        <v>-14782.51</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>0</v>
+        <v>9343.35</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>0</v>
+        <v>-13861.77</v>
       </c>
       <c r="K102" s="34" t="n">
-        <v>1159</v>
+        <v>-21112.7</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>19550.48</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>-29140.26</v>
       </c>
       <c r="P102" s="9" t="n"/>
       <c r="U102" s="9" t="n"/>
       <c r="Z102" s="9" t="n"/>
-      <c r="AB102" s="5" t="n"/>
+      <c r="AA102" s="18" t="n">
+        <v>48345.58</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>174502.68</v>
+      </c>
       <c r="AC102" s="10" t="n"/>
       <c r="AD102" s="10" t="n"/>
       <c r="AE102" s="11" t="n"/>
@@ -15801,37 +15641,40 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E103" s="18" t="n">
-        <v>35000</v>
+        <v>-9.16</v>
       </c>
       <c r="F103" s="9" t="n"/>
       <c r="G103" s="18" t="n">
-        <v>15000</v>
+        <v>-6.37</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>15000</v>
+        <v>35.44</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>35000</v>
+        <v>-22.2</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>19202.1</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="K103" s="34" t="n">
-        <v>84202.10000000001</v>
+        <v>-65.56</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>31000</v>
+        <v>-45.8</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>30100</v>
+        <v>-55.2</v>
       </c>
       <c r="P103" s="9" t="n"/>
       <c r="U103" s="9" t="n"/>
       <c r="Z103" s="9" t="n"/>
+      <c r="AA103" s="18" t="n">
+        <v>-1606.38</v>
+      </c>
       <c r="AB103" s="5" t="n"/>
       <c r="AC103" s="10" t="n"/>
       <c r="AD103" s="10" t="n"/>
@@ -15853,41 +15696,43 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E104" s="18" t="n">
-        <v>357.74</v>
+        <v>-2787.46</v>
       </c>
       <c r="F104" s="9" t="n"/>
       <c r="G104" s="18" t="n">
-        <v>450.71</v>
+        <v>1473.28</v>
       </c>
       <c r="H104" s="18" t="n">
-        <v>491.94</v>
+        <v>-3699.09</v>
       </c>
       <c r="I104" s="18" t="n">
-        <v>458.7</v>
+        <v>-38914.88</v>
       </c>
       <c r="J104" s="18" t="n">
-        <v>485.05</v>
+        <v>-13368.48</v>
       </c>
       <c r="K104" s="34" t="n">
-        <v>1886.4</v>
+        <v>-54509.17</v>
       </c>
       <c r="L104" s="18" t="n">
-        <v>488.81</v>
+        <v>-3086.88</v>
       </c>
       <c r="M104" s="18" t="n">
-        <v>517.48</v>
+        <v>-11699.19</v>
       </c>
       <c r="P104" s="9" t="n"/>
       <c r="U104" s="9" t="n"/>
       <c r="Z104" s="9" t="n"/>
       <c r="AA104" s="18" t="n">
-        <v>588.55</v>
-      </c>
-      <c r="AB104" s="5" t="n"/>
+        <v>-265353.43</v>
+      </c>
+      <c r="AB104" s="19" t="n">
+        <v>-34521.93</v>
+      </c>
       <c r="AC104" s="10" t="n"/>
       <c r="AD104" s="10" t="n"/>
       <c r="AE104" s="11" t="n"/>
@@ -15908,39 +15753,31 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-11818.92</v>
+        <v>0</v>
       </c>
       <c r="F105" s="9" t="n"/>
-      <c r="G105" s="18" t="n">
-        <v>9795.629999999999</v>
-      </c>
-      <c r="H105" s="18" t="n">
-        <v>-9266.34</v>
-      </c>
       <c r="I105" s="18" t="n">
-        <v>36885.15</v>
+        <v>3.91</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-36927.46</v>
-      </c>
-      <c r="K105" s="34" t="n">
-        <v>486.98</v>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="K105" s="9" t="n"/>
       <c r="L105" s="18" t="n">
-        <v>11812.3</v>
+        <v>49.22</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-33287.89</v>
+        <v>15.92</v>
       </c>
       <c r="P105" s="9" t="n"/>
       <c r="U105" s="9" t="n"/>
       <c r="Z105" s="9" t="n"/>
       <c r="AA105" s="18" t="n">
-        <v>-226710.47</v>
+        <v>1.82</v>
       </c>
       <c r="AB105" s="5" t="n"/>
       <c r="AC105" s="10" t="n"/>
@@ -15963,43 +15800,18 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E106" s="18" t="n">
-        <v>-11818.92</v>
+        <v>178.02</v>
       </c>
       <c r="F106" s="9" t="n"/>
-      <c r="G106" s="18" t="n">
-        <v>63867.89</v>
-      </c>
-      <c r="H106" s="18" t="n">
-        <v>-9266.33</v>
-      </c>
-      <c r="I106" s="18" t="n">
-        <v>36885.15</v>
-      </c>
-      <c r="J106" s="18" t="n">
-        <v>-36927.46</v>
-      </c>
-      <c r="K106" s="34" t="n">
-        <v>54559.25</v>
-      </c>
-      <c r="L106" s="18" t="n">
-        <v>66371.55</v>
-      </c>
-      <c r="M106" s="18" t="n">
-        <v>-33287.89</v>
-      </c>
+      <c r="K106" s="9" t="n"/>
       <c r="P106" s="9" t="n"/>
       <c r="U106" s="9" t="n"/>
       <c r="Z106" s="9" t="n"/>
-      <c r="AA106" s="18" t="n">
-        <v>49997.56</v>
-      </c>
-      <c r="AB106" s="19" t="n">
-        <v>113638.39</v>
-      </c>
+      <c r="AB106" s="5" t="n"/>
       <c r="AC106" s="10" t="n"/>
       <c r="AD106" s="10" t="n"/>
       <c r="AE106" s="11" t="n"/>
@@ -16020,26 +15832,40 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>2782.22</v>
       </c>
       <c r="F107" s="9" t="n"/>
+      <c r="G107" s="18" t="n">
+        <v>1716.49</v>
+      </c>
+      <c r="H107" s="18" t="n">
+        <v>1999.55</v>
+      </c>
       <c r="I107" s="18" t="n">
-        <v>3514.2</v>
+        <v>2897.04</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>4013.93</v>
-      </c>
-      <c r="K107" s="9" t="n"/>
+        <v>2405.25</v>
+      </c>
+      <c r="K107" s="34" t="n">
+        <v>9018.33</v>
+      </c>
       <c r="L107" s="18" t="n">
-        <v>4013.94</v>
+        <v>4536.04</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>51013.93</v>
+        <v>11065.58</v>
       </c>
       <c r="P107" s="9" t="n"/>
       <c r="U107" s="9" t="n"/>
       <c r="Z107" s="9" t="n"/>
+      <c r="AA107" s="18" t="n">
+        <v>23598.89</v>
+      </c>
       <c r="AB107" s="5" t="n"/>
       <c r="AC107" s="10" t="n"/>
       <c r="AD107" s="10" t="n"/>
@@ -16061,17 +15887,40 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>2916.22</v>
       </c>
       <c r="F108" s="9" t="n"/>
+      <c r="G108" s="18" t="n">
+        <v>1730.49</v>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>2129.35</v>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>3194.89</v>
+      </c>
       <c r="J108" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="9" t="n"/>
+        <v>2601.13</v>
+      </c>
+      <c r="K108" s="34" t="n">
+        <v>9655.860000000001</v>
+      </c>
+      <c r="L108" s="18" t="n">
+        <v>4539.04</v>
+      </c>
+      <c r="M108" s="18" t="n">
+        <v>11062.58</v>
+      </c>
       <c r="P108" s="9" t="n"/>
       <c r="U108" s="9" t="n"/>
       <c r="Z108" s="9" t="n"/>
+      <c r="AA108" s="18" t="n">
+        <v>24939.45</v>
+      </c>
       <c r="AB108" s="5" t="n"/>
       <c r="AC108" s="10" t="n"/>
       <c r="AD108" s="10" t="n"/>
@@ -16093,17 +15942,37 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>134</v>
       </c>
       <c r="F109" s="9" t="n"/>
+      <c r="G109" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="H109" s="18" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="I109" s="18" t="n">
+        <v>297.85</v>
+      </c>
       <c r="J109" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="9" t="n"/>
+        <v>195.88</v>
+      </c>
+      <c r="K109" s="34" t="n">
+        <v>637.53</v>
+      </c>
+      <c r="L109" s="18" t="n">
+        <v>3</v>
+      </c>
       <c r="P109" s="9" t="n"/>
       <c r="U109" s="9" t="n"/>
       <c r="Z109" s="9" t="n"/>
+      <c r="AA109" s="18" t="n">
+        <v>1340.56</v>
+      </c>
       <c r="AB109" s="5" t="n"/>
       <c r="AC109" s="10" t="n"/>
       <c r="AD109" s="10" t="n"/>
@@ -16125,18 +15994,43 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="n">
+        <v>724.25</v>
       </c>
       <c r="F110" s="9" t="n"/>
-      <c r="K110" s="9" t="n"/>
+      <c r="G110" s="18" t="n">
+        <v>10235.29</v>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>8981.059999999999</v>
+      </c>
+      <c r="I110" s="18" t="n">
+        <v>65245.88</v>
+      </c>
+      <c r="J110" s="18" t="n">
+        <v>-7709.98</v>
+      </c>
+      <c r="K110" s="34" t="n">
+        <v>76752.25</v>
+      </c>
+      <c r="L110" s="18" t="n">
+        <v>-4502.75</v>
+      </c>
+      <c r="M110" s="18" t="n">
+        <v>7267.09</v>
+      </c>
       <c r="P110" s="9" t="n"/>
       <c r="U110" s="9" t="n"/>
       <c r="Z110" s="9" t="n"/>
       <c r="AA110" s="18" t="n">
-        <v>3251.68</v>
-      </c>
-      <c r="AB110" s="5" t="n"/>
+        <v>-968</v>
+      </c>
+      <c r="AB110" s="19" t="n">
+        <v>-43836.32</v>
+      </c>
       <c r="AC110" s="10" t="n"/>
       <c r="AD110" s="10" t="n"/>
       <c r="AE110" s="11" t="n"/>
@@ -16157,17 +16051,37 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>35000</v>
       </c>
       <c r="F111" s="9" t="n"/>
-      <c r="K111" s="9" t="n"/>
+      <c r="G111" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H111" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I111" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J111" s="18" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K111" s="34" t="n">
+        <v>81000</v>
+      </c>
+      <c r="L111" s="18" t="n">
+        <v>31000</v>
+      </c>
+      <c r="M111" s="18" t="n">
+        <v>49000</v>
+      </c>
       <c r="P111" s="9" t="n"/>
       <c r="U111" s="9" t="n"/>
       <c r="Z111" s="9" t="n"/>
-      <c r="AA111" s="18" t="n">
-        <v>-379.45</v>
-      </c>
       <c r="AB111" s="5" t="n"/>
       <c r="AC111" s="10" t="n"/>
       <c r="AD111" s="10" t="n"/>
@@ -16183,6 +16097,440 @@
       <c r="AN111" s="10" t="n"/>
       <c r="AO111" s="11" t="n"/>
     </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="n">
+        <v>1082</v>
+      </c>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="18" t="n">
+        <v>686</v>
+      </c>
+      <c r="H112" s="18" t="n">
+        <v>473</v>
+      </c>
+      <c r="I112" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="34" t="n">
+        <v>1159</v>
+      </c>
+      <c r="P112" s="9" t="n"/>
+      <c r="U112" s="9" t="n"/>
+      <c r="Z112" s="9" t="n"/>
+      <c r="AB112" s="5" t="n"/>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="11" t="n"/>
+      <c r="AK112" s="10" t="n"/>
+      <c r="AL112" s="10" t="n"/>
+      <c r="AM112" s="10" t="n"/>
+      <c r="AN112" s="10" t="n"/>
+      <c r="AO112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H113" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I113" s="18" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J113" s="18" t="n">
+        <v>19202.1</v>
+      </c>
+      <c r="K113" s="34" t="n">
+        <v>84202.10000000001</v>
+      </c>
+      <c r="L113" s="18" t="n">
+        <v>31000</v>
+      </c>
+      <c r="M113" s="18" t="n">
+        <v>30100</v>
+      </c>
+      <c r="P113" s="9" t="n"/>
+      <c r="U113" s="9" t="n"/>
+      <c r="Z113" s="9" t="n"/>
+      <c r="AB113" s="5" t="n"/>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="11" t="n"/>
+      <c r="AK113" s="10" t="n"/>
+      <c r="AL113" s="10" t="n"/>
+      <c r="AM113" s="10" t="n"/>
+      <c r="AN113" s="10" t="n"/>
+      <c r="AO113" s="11" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="18" t="n">
+        <v>450.71</v>
+      </c>
+      <c r="H114" s="18" t="n">
+        <v>491.94</v>
+      </c>
+      <c r="I114" s="18" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="J114" s="18" t="n">
+        <v>485.05</v>
+      </c>
+      <c r="K114" s="34" t="n">
+        <v>1886.4</v>
+      </c>
+      <c r="L114" s="18" t="n">
+        <v>488.81</v>
+      </c>
+      <c r="M114" s="18" t="n">
+        <v>517.48</v>
+      </c>
+      <c r="P114" s="9" t="n"/>
+      <c r="U114" s="9" t="n"/>
+      <c r="Z114" s="9" t="n"/>
+      <c r="AA114" s="18" t="n">
+        <v>588.55</v>
+      </c>
+      <c r="AB114" s="5" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="11" t="n"/>
+      <c r="AK114" s="10" t="n"/>
+      <c r="AL114" s="10" t="n"/>
+      <c r="AM114" s="10" t="n"/>
+      <c r="AN114" s="10" t="n"/>
+      <c r="AO114" s="11" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="n">
+        <v>-11818.92</v>
+      </c>
+      <c r="F115" s="9" t="n"/>
+      <c r="G115" s="18" t="n">
+        <v>9795.629999999999</v>
+      </c>
+      <c r="H115" s="18" t="n">
+        <v>-9266.34</v>
+      </c>
+      <c r="I115" s="18" t="n">
+        <v>36885.15</v>
+      </c>
+      <c r="J115" s="18" t="n">
+        <v>-36927.46</v>
+      </c>
+      <c r="K115" s="34" t="n">
+        <v>486.98</v>
+      </c>
+      <c r="L115" s="18" t="n">
+        <v>11812.3</v>
+      </c>
+      <c r="M115" s="18" t="n">
+        <v>-33287.89</v>
+      </c>
+      <c r="P115" s="9" t="n"/>
+      <c r="U115" s="9" t="n"/>
+      <c r="Z115" s="9" t="n"/>
+      <c r="AA115" s="18" t="n">
+        <v>-226710.47</v>
+      </c>
+      <c r="AB115" s="5" t="n"/>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="11" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="11" t="n"/>
+      <c r="AK115" s="10" t="n"/>
+      <c r="AL115" s="10" t="n"/>
+      <c r="AM115" s="10" t="n"/>
+      <c r="AN115" s="10" t="n"/>
+      <c r="AO115" s="11" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="n">
+        <v>-11818.92</v>
+      </c>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="18" t="n">
+        <v>63867.89</v>
+      </c>
+      <c r="H116" s="18" t="n">
+        <v>-9266.33</v>
+      </c>
+      <c r="I116" s="18" t="n">
+        <v>36885.15</v>
+      </c>
+      <c r="J116" s="18" t="n">
+        <v>-36927.46</v>
+      </c>
+      <c r="K116" s="34" t="n">
+        <v>54559.25</v>
+      </c>
+      <c r="L116" s="18" t="n">
+        <v>66371.55</v>
+      </c>
+      <c r="M116" s="18" t="n">
+        <v>-33287.89</v>
+      </c>
+      <c r="P116" s="9" t="n"/>
+      <c r="U116" s="9" t="n"/>
+      <c r="Z116" s="9" t="n"/>
+      <c r="AA116" s="18" t="n">
+        <v>49997.56</v>
+      </c>
+      <c r="AB116" s="19" t="n">
+        <v>113638.39</v>
+      </c>
+      <c r="AC116" s="10" t="n"/>
+      <c r="AD116" s="10" t="n"/>
+      <c r="AE116" s="11" t="n"/>
+      <c r="AF116" s="10" t="n"/>
+      <c r="AG116" s="10" t="n"/>
+      <c r="AH116" s="10" t="n"/>
+      <c r="AI116" s="10" t="n"/>
+      <c r="AJ116" s="11" t="n"/>
+      <c r="AK116" s="10" t="n"/>
+      <c r="AL116" s="10" t="n"/>
+      <c r="AM116" s="10" t="n"/>
+      <c r="AN116" s="10" t="n"/>
+      <c r="AO116" s="11" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="n"/>
+      <c r="I117" s="18" t="n">
+        <v>3514.2</v>
+      </c>
+      <c r="J117" s="18" t="n">
+        <v>4013.93</v>
+      </c>
+      <c r="K117" s="9" t="n"/>
+      <c r="L117" s="18" t="n">
+        <v>4013.94</v>
+      </c>
+      <c r="M117" s="18" t="n">
+        <v>51013.93</v>
+      </c>
+      <c r="P117" s="9" t="n"/>
+      <c r="U117" s="9" t="n"/>
+      <c r="Z117" s="9" t="n"/>
+      <c r="AB117" s="5" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="11" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="11" t="n"/>
+      <c r="AK117" s="10" t="n"/>
+      <c r="AL117" s="10" t="n"/>
+      <c r="AM117" s="10" t="n"/>
+      <c r="AN117" s="10" t="n"/>
+      <c r="AO117" s="11" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="n"/>
+      <c r="J118" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="9" t="n"/>
+      <c r="P118" s="9" t="n"/>
+      <c r="U118" s="9" t="n"/>
+      <c r="Z118" s="9" t="n"/>
+      <c r="AB118" s="5" t="n"/>
+      <c r="AC118" s="10" t="n"/>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="11" t="n"/>
+      <c r="AF118" s="10" t="n"/>
+      <c r="AG118" s="10" t="n"/>
+      <c r="AH118" s="10" t="n"/>
+      <c r="AI118" s="10" t="n"/>
+      <c r="AJ118" s="11" t="n"/>
+      <c r="AK118" s="10" t="n"/>
+      <c r="AL118" s="10" t="n"/>
+      <c r="AM118" s="10" t="n"/>
+      <c r="AN118" s="10" t="n"/>
+      <c r="AO118" s="11" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n"/>
+      <c r="J119" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="9" t="n"/>
+      <c r="P119" s="9" t="n"/>
+      <c r="U119" s="9" t="n"/>
+      <c r="Z119" s="9" t="n"/>
+      <c r="AB119" s="5" t="n"/>
+      <c r="AC119" s="10" t="n"/>
+      <c r="AD119" s="10" t="n"/>
+      <c r="AE119" s="11" t="n"/>
+      <c r="AF119" s="10" t="n"/>
+      <c r="AG119" s="10" t="n"/>
+      <c r="AH119" s="10" t="n"/>
+      <c r="AI119" s="10" t="n"/>
+      <c r="AJ119" s="11" t="n"/>
+      <c r="AK119" s="10" t="n"/>
+      <c r="AL119" s="10" t="n"/>
+      <c r="AM119" s="10" t="n"/>
+      <c r="AN119" s="10" t="n"/>
+      <c r="AO119" s="11" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="n"/>
+      <c r="K120" s="9" t="n"/>
+      <c r="P120" s="9" t="n"/>
+      <c r="U120" s="9" t="n"/>
+      <c r="Z120" s="9" t="n"/>
+      <c r="AA120" s="18" t="n">
+        <v>3251.68</v>
+      </c>
+      <c r="AB120" s="5" t="n"/>
+      <c r="AC120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="11" t="n"/>
+      <c r="AF120" s="10" t="n"/>
+      <c r="AG120" s="10" t="n"/>
+      <c r="AH120" s="10" t="n"/>
+      <c r="AI120" s="10" t="n"/>
+      <c r="AJ120" s="11" t="n"/>
+      <c r="AK120" s="10" t="n"/>
+      <c r="AL120" s="10" t="n"/>
+      <c r="AM120" s="10" t="n"/>
+      <c r="AN120" s="10" t="n"/>
+      <c r="AO120" s="11" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="n"/>
+      <c r="K121" s="9" t="n"/>
+      <c r="P121" s="9" t="n"/>
+      <c r="U121" s="9" t="n"/>
+      <c r="Z121" s="9" t="n"/>
+      <c r="AA121" s="18" t="n">
+        <v>-379.45</v>
+      </c>
+      <c r="AB121" s="5" t="n"/>
+      <c r="AC121" s="10" t="n"/>
+      <c r="AD121" s="10" t="n"/>
+      <c r="AE121" s="11" t="n"/>
+      <c r="AF121" s="10" t="n"/>
+      <c r="AG121" s="10" t="n"/>
+      <c r="AH121" s="10" t="n"/>
+      <c r="AI121" s="10" t="n"/>
+      <c r="AJ121" s="11" t="n"/>
+      <c r="AK121" s="10" t="n"/>
+      <c r="AL121" s="10" t="n"/>
+      <c r="AM121" s="10" t="n"/>
+      <c r="AN121" s="10" t="n"/>
+      <c r="AO121" s="11" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16194,7 +16542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO110"/>
+  <dimension ref="A1:AO120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16442,7 +16790,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23623,79 +23971,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>-9770.23</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="G89" s="18" t="n">
-        <v>-1721.07</v>
-      </c>
-      <c r="H89" s="18" t="n">
-        <v>-14610.2</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <v>9535.18</v>
-      </c>
-      <c r="J89" s="18" t="n">
-        <v>-13644.79</v>
-      </c>
-      <c r="K89" s="34" t="n">
-        <v>-20440.88</v>
-      </c>
-      <c r="L89" s="18" t="n">
-        <v>19613.07</v>
-      </c>
-      <c r="M89" s="18" t="n">
-        <v>-29204.48</v>
-      </c>
-      <c r="N89" s="18" t="n">
-        <v>-384.07</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>80127.59</v>
-      </c>
-      <c r="P89" s="34" t="n">
-        <v>70152.11</v>
-      </c>
-      <c r="Q89" s="18" t="n">
-        <v>-14455.7</v>
-      </c>
-      <c r="R89" s="18" t="n">
-        <v>37443.6</v>
-      </c>
-      <c r="S89" s="18" t="n">
-        <v>-4336.27</v>
-      </c>
-      <c r="T89" s="18" t="n">
-        <v>71724.07000000001</v>
-      </c>
-      <c r="U89" s="34" t="n">
-        <v>90375.7</v>
-      </c>
+      <c r="K89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
+      <c r="U89" s="9" t="n"/>
       <c r="V89" s="18" t="n">
-        <v>46058.61</v>
+        <v>1098.71</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>169896.82</v>
+        <v>2221.01</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>34713.08</v>
-      </c>
-      <c r="Y89" s="18" t="n">
-        <v>79650.17</v>
-      </c>
-      <c r="Z89" s="34" t="n">
-        <v>330318.68</v>
-      </c>
-      <c r="AA89" s="18" t="n">
-        <v>48835.01</v>
-      </c>
-      <c r="AB89" s="19" t="n">
-        <v>182471.81</v>
-      </c>
+        <v>3447.36</v>
+      </c>
+      <c r="Z89" s="9" t="n"/>
+      <c r="AB89" s="5" t="n"/>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="11" t="n"/>
@@ -23716,76 +24009,23 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>-9.16</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="18" t="n">
-        <v>-6.37</v>
-      </c>
-      <c r="H90" s="18" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="I90" s="18" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>-72.43000000000001</v>
-      </c>
-      <c r="K90" s="34" t="n">
-        <v>-65.56</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>-45.8</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>-55.2</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>-76.29000000000001</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="P90" s="34" t="n">
-        <v>-173.61</v>
-      </c>
-      <c r="Q90" s="18" t="n">
-        <v>-156.07</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="S90" s="18" t="n">
-        <v>-716.99</v>
-      </c>
-      <c r="T90" s="18" t="n">
-        <v>-310.5</v>
-      </c>
-      <c r="U90" s="34" t="n">
-        <v>-1158.58</v>
-      </c>
+      <c r="K90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
+      <c r="U90" s="9" t="n"/>
       <c r="V90" s="18" t="n">
-        <v>-325.24</v>
+        <v>930.34</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>-585.8099999999999</v>
+        <v>852.0700000000001</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="Y90" s="18" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="Z90" s="34" t="n">
-        <v>-912.16</v>
-      </c>
-      <c r="AA90" s="18" t="n">
-        <v>-1606.38</v>
-      </c>
+        <v>761.66</v>
+      </c>
+      <c r="Z90" s="9" t="n"/>
       <c r="AB90" s="5" t="n"/>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -23807,79 +24047,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>-2787.46</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="G91" s="18" t="n">
-        <v>1640.88</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>-4083.5</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>-38917.21</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>-16511.7</v>
-      </c>
-      <c r="K91" s="34" t="n">
-        <v>-57871.53</v>
-      </c>
-      <c r="L91" s="18" t="n">
-        <v>-3086.88</v>
-      </c>
-      <c r="M91" s="18" t="n">
-        <v>-11699.19</v>
-      </c>
-      <c r="N91" s="18" t="n">
-        <v>-9012.129999999999</v>
-      </c>
-      <c r="O91" s="18" t="n">
-        <v>-6481.14</v>
-      </c>
-      <c r="P91" s="34" t="n">
-        <v>-30279.34</v>
-      </c>
-      <c r="Q91" s="18" t="n">
-        <v>31045.05</v>
-      </c>
-      <c r="R91" s="18" t="n">
-        <v>-22379.04</v>
-      </c>
-      <c r="S91" s="18" t="n">
-        <v>-8850.68</v>
-      </c>
-      <c r="T91" s="18" t="n">
-        <v>-4129.06</v>
-      </c>
-      <c r="U91" s="34" t="n">
-        <v>-4313.73</v>
-      </c>
+      <c r="K91" s="9" t="n"/>
+      <c r="P91" s="9" t="n"/>
+      <c r="U91" s="9" t="n"/>
       <c r="V91" s="18" t="n">
-        <v>-65613.69</v>
+        <v>8268.01</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>-78391.57000000001</v>
+        <v>9411.639999999999</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>-20306.37</v>
-      </c>
-      <c r="Y91" s="18" t="n">
-        <v>3191.67</v>
-      </c>
-      <c r="Z91" s="34" t="n">
-        <v>-161119.96</v>
-      </c>
-      <c r="AA91" s="18" t="n">
-        <v>-278449.16</v>
-      </c>
-      <c r="AB91" s="19" t="n">
-        <v>-31131.53</v>
-      </c>
+        <v>15093.09</v>
+      </c>
+      <c r="Z91" s="9" t="n"/>
+      <c r="AB91" s="5" t="n"/>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="11" t="n"/>
@@ -23900,46 +24085,23 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>0</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="I92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="K92" s="9" t="n"/>
-      <c r="L92" s="18" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="P92" s="34" t="n">
-        <v>212.39</v>
-      </c>
-      <c r="T92" s="18" t="n">
-        <v>1.89</v>
-      </c>
+      <c r="P92" s="9" t="n"/>
       <c r="U92" s="9" t="n"/>
-      <c r="Y92" s="18" t="n">
-        <v>141.01</v>
+      <c r="V92" s="18" t="n">
+        <v>9280.440000000001</v>
+      </c>
+      <c r="W92" s="18" t="n">
+        <v>26079.92</v>
+      </c>
+      <c r="X92" s="18" t="n">
+        <v>13161.58</v>
       </c>
       <c r="Z92" s="9" t="n"/>
-      <c r="AA92" s="18" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AB92" s="5" t="n"/>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -23961,18 +24123,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>178.02</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="K93" s="9" t="n"/>
       <c r="P93" s="9" t="n"/>
       <c r="U93" s="9" t="n"/>
+      <c r="V93" s="18" t="n">
+        <v>1394.36</v>
+      </c>
+      <c r="W93" s="18" t="n">
+        <v>2068.02</v>
+      </c>
       <c r="X93" s="18" t="n">
-        <v>140.31</v>
+        <v>1393.4</v>
       </c>
       <c r="Z93" s="9" t="n"/>
       <c r="AB93" s="5" t="n"/>
@@ -23996,76 +24161,23 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>2782.22</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="G94" s="18" t="n">
-        <v>1548.89</v>
-      </c>
-      <c r="H94" s="18" t="n">
-        <v>1999.2</v>
-      </c>
-      <c r="I94" s="18" t="n">
-        <v>2895.45</v>
-      </c>
-      <c r="J94" s="18" t="n">
-        <v>2405.48</v>
-      </c>
-      <c r="K94" s="34" t="n">
-        <v>8849.02</v>
-      </c>
-      <c r="L94" s="18" t="n">
-        <v>4536.04</v>
-      </c>
-      <c r="M94" s="18" t="n">
-        <v>11065.58</v>
-      </c>
-      <c r="N94" s="18" t="n">
-        <v>9036.9</v>
-      </c>
-      <c r="O94" s="18" t="n">
-        <v>6425.72</v>
-      </c>
-      <c r="P94" s="34" t="n">
-        <v>31064.24</v>
-      </c>
-      <c r="Q94" s="18" t="n">
-        <v>6737.19</v>
-      </c>
-      <c r="R94" s="18" t="n">
-        <v>15981.3</v>
-      </c>
-      <c r="S94" s="18" t="n">
-        <v>20599.22</v>
-      </c>
-      <c r="T94" s="18" t="n">
-        <v>7686.07</v>
-      </c>
-      <c r="U94" s="34" t="n">
-        <v>51003.78</v>
-      </c>
+      <c r="K94" s="9" t="n"/>
+      <c r="P94" s="9" t="n"/>
+      <c r="U94" s="9" t="n"/>
       <c r="V94" s="18" t="n">
-        <v>5356.11</v>
+        <v>110.46</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>3434.1</v>
+        <v>8006.3</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>9098.16</v>
-      </c>
-      <c r="Y94" s="18" t="n">
-        <v>15401.44</v>
-      </c>
-      <c r="Z94" s="34" t="n">
-        <v>33289.81</v>
-      </c>
-      <c r="AA94" s="18" t="n">
-        <v>23598.89</v>
-      </c>
+        <v>-6376.12</v>
+      </c>
+      <c r="Z94" s="9" t="n"/>
       <c r="AB94" s="5" t="n"/>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -24087,76 +24199,23 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>2916.22</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F95" s="9" t="n"/>
-      <c r="G95" s="18" t="n">
-        <v>1562.89</v>
-      </c>
-      <c r="H95" s="18" t="n">
-        <v>2129</v>
-      </c>
-      <c r="I95" s="18" t="n">
-        <v>3193.3</v>
-      </c>
-      <c r="J95" s="18" t="n">
-        <v>2601.36</v>
-      </c>
-      <c r="K95" s="34" t="n">
-        <v>9486.549999999999</v>
-      </c>
-      <c r="L95" s="18" t="n">
-        <v>4539.04</v>
-      </c>
-      <c r="M95" s="18" t="n">
-        <v>11062.58</v>
-      </c>
-      <c r="N95" s="18" t="n">
-        <v>9036.9</v>
-      </c>
-      <c r="O95" s="18" t="n">
-        <v>6765.8</v>
-      </c>
-      <c r="P95" s="34" t="n">
-        <v>31404.32</v>
-      </c>
-      <c r="Q95" s="18" t="n">
-        <v>6737.19</v>
-      </c>
-      <c r="R95" s="18" t="n">
-        <v>16105.91</v>
-      </c>
-      <c r="S95" s="18" t="n">
-        <v>21435.41</v>
-      </c>
-      <c r="T95" s="18" t="n">
-        <v>10223.38</v>
-      </c>
-      <c r="U95" s="34" t="n">
-        <v>54501.89</v>
-      </c>
+      <c r="K95" s="9" t="n"/>
+      <c r="P95" s="9" t="n"/>
+      <c r="U95" s="9" t="n"/>
       <c r="V95" s="18" t="n">
-        <v>6838.01</v>
+        <v>6734.65</v>
       </c>
       <c r="W95" s="18" t="n">
-        <v>4076.3</v>
+        <v>164986.15</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>9986.15</v>
-      </c>
-      <c r="Y95" s="18" t="n">
-        <v>17961.31</v>
-      </c>
-      <c r="Z95" s="34" t="n">
-        <v>38861.77</v>
-      </c>
-      <c r="AA95" s="18" t="n">
-        <v>24939.45</v>
-      </c>
+        <v>-90049.82000000001</v>
+      </c>
+      <c r="Z95" s="9" t="n"/>
       <c r="AB95" s="5" t="n"/>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -24178,57 +24237,23 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>134</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="G96" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="H96" s="18" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="I96" s="18" t="n">
-        <v>297.85</v>
-      </c>
-      <c r="J96" s="18" t="n">
-        <v>195.88</v>
-      </c>
-      <c r="K96" s="34" t="n">
-        <v>637.53</v>
-      </c>
-      <c r="L96" s="18" t="n">
-        <v>3</v>
-      </c>
+      <c r="K96" s="9" t="n"/>
       <c r="P96" s="9" t="n"/>
-      <c r="S96" s="18" t="n">
-        <v>836.1900000000001</v>
-      </c>
-      <c r="T96" s="18" t="n">
-        <v>2537.31</v>
-      </c>
       <c r="U96" s="9" t="n"/>
       <c r="V96" s="18" t="n">
-        <v>1481.9</v>
+        <v>32705.85</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>642.2</v>
+        <v>-24525.74</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>887.99</v>
-      </c>
-      <c r="Y96" s="18" t="n">
-        <v>2559.87</v>
-      </c>
-      <c r="Z96" s="34" t="n">
-        <v>5571.96</v>
-      </c>
-      <c r="AA96" s="18" t="n">
-        <v>1340.56</v>
-      </c>
+        <v>9919.02</v>
+      </c>
+      <c r="Z96" s="9" t="n"/>
       <c r="AB96" s="5" t="n"/>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -24250,79 +24275,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E97" s="18" t="n">
-        <v>724.25</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F97" s="9" t="n"/>
-      <c r="G97" s="18" t="n">
-        <v>10235.29</v>
-      </c>
-      <c r="H97" s="18" t="n">
-        <v>8981.059999999999</v>
-      </c>
-      <c r="I97" s="18" t="n">
-        <v>65245.88</v>
-      </c>
-      <c r="J97" s="18" t="n">
-        <v>-4507.88</v>
-      </c>
-      <c r="K97" s="34" t="n">
-        <v>79954.35000000001</v>
-      </c>
-      <c r="L97" s="18" t="n">
-        <v>-4502.75</v>
-      </c>
-      <c r="M97" s="18" t="n">
-        <v>7267.09</v>
-      </c>
-      <c r="N97" s="18" t="n">
-        <v>24158.47</v>
-      </c>
-      <c r="O97" s="18" t="n">
-        <v>-18166.87</v>
-      </c>
-      <c r="P97" s="34" t="n">
-        <v>8755.940000000001</v>
-      </c>
-      <c r="Q97" s="18" t="n">
-        <v>86685.44</v>
-      </c>
-      <c r="R97" s="18" t="n">
-        <v>-122797.81</v>
-      </c>
-      <c r="S97" s="18" t="n">
-        <v>-4727.67</v>
-      </c>
-      <c r="T97" s="18" t="n">
-        <v>-16454.41</v>
-      </c>
-      <c r="U97" s="34" t="n">
-        <v>-57294.45</v>
-      </c>
+      <c r="K97" s="9" t="n"/>
+      <c r="P97" s="9" t="n"/>
+      <c r="U97" s="9" t="n"/>
       <c r="V97" s="18" t="n">
-        <v>9407.040000000001</v>
+        <v>168.37</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>-10582.04</v>
+        <v>1368.94</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>-541.2</v>
-      </c>
-      <c r="Y97" s="18" t="n">
-        <v>-20548.96</v>
-      </c>
-      <c r="Z97" s="34" t="n">
-        <v>-22265.16</v>
-      </c>
-      <c r="AA97" s="18" t="n">
-        <v>-968</v>
-      </c>
-      <c r="AB97" s="19" t="n">
-        <v>-41153.13</v>
-      </c>
+        <v>2685.7</v>
+      </c>
+      <c r="Z97" s="9" t="n"/>
+      <c r="AB97" s="5" t="n"/>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
       <c r="AE97" s="11" t="n"/>
@@ -24343,52 +24313,18 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E98" s="18" t="n">
-        <v>35000</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F98" s="9" t="n"/>
-      <c r="G98" s="18" t="n">
-        <v>25000</v>
-      </c>
-      <c r="H98" s="18" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I98" s="18" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J98" s="18" t="n">
-        <v>16000</v>
-      </c>
-      <c r="K98" s="34" t="n">
-        <v>81000</v>
-      </c>
-      <c r="L98" s="18" t="n">
-        <v>31000</v>
-      </c>
-      <c r="M98" s="18" t="n">
-        <v>49000</v>
-      </c>
-      <c r="N98" s="18" t="n">
-        <v>41000</v>
-      </c>
-      <c r="O98" s="18" t="n">
-        <v>6000</v>
-      </c>
-      <c r="P98" s="34" t="n">
-        <v>127000</v>
-      </c>
-      <c r="T98" s="18" t="n">
-        <v>22000</v>
-      </c>
+      <c r="K98" s="9" t="n"/>
+      <c r="P98" s="9" t="n"/>
       <c r="U98" s="9" t="n"/>
+      <c r="W98" s="18" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="X98" s="18" t="n">
         <v>0</v>
-      </c>
-      <c r="Y98" s="18" t="n">
-        <v>30000</v>
       </c>
       <c r="Z98" s="9" t="n"/>
       <c r="AB98" s="5" t="n"/>
@@ -24412,49 +24348,79 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E99" s="18" t="n">
-        <v>1082</v>
+        <v>-9770.23</v>
       </c>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="18" t="n">
-        <v>686</v>
+        <v>-1721.07</v>
       </c>
       <c r="H99" s="18" t="n">
-        <v>473</v>
+        <v>-14610.2</v>
       </c>
       <c r="I99" s="18" t="n">
-        <v>0</v>
+        <v>9535.18</v>
       </c>
       <c r="J99" s="18" t="n">
-        <v>0</v>
+        <v>-13644.79</v>
       </c>
       <c r="K99" s="34" t="n">
-        <v>1159</v>
-      </c>
-      <c r="P99" s="9" t="n"/>
+        <v>-20440.88</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>19613.07</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>-29204.48</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>-384.07</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>80127.59</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>70152.11</v>
+      </c>
+      <c r="Q99" s="18" t="n">
+        <v>-14455.7</v>
+      </c>
+      <c r="R99" s="18" t="n">
+        <v>37443.6</v>
+      </c>
+      <c r="S99" s="18" t="n">
+        <v>-4336.27</v>
+      </c>
       <c r="T99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" s="9" t="n"/>
+        <v>71724.07000000001</v>
+      </c>
+      <c r="U99" s="34" t="n">
+        <v>90375.7</v>
+      </c>
       <c r="V99" s="18" t="n">
-        <v>10000</v>
+        <v>46058.61</v>
       </c>
       <c r="W99" s="18" t="n">
-        <v>0</v>
+        <v>169896.82</v>
       </c>
       <c r="X99" s="18" t="n">
-        <v>0</v>
+        <v>34713.08</v>
       </c>
       <c r="Y99" s="18" t="n">
-        <v>0</v>
+        <v>79650.17</v>
       </c>
       <c r="Z99" s="34" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB99" s="5" t="n"/>
+        <v>330318.68</v>
+      </c>
+      <c r="AA99" s="18" t="n">
+        <v>48835.01</v>
+      </c>
+      <c r="AB99" s="19" t="n">
+        <v>182471.81</v>
+      </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
       <c r="AE99" s="11" t="n"/>
@@ -24475,72 +24441,75 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E100" s="18" t="n">
-        <v>35000</v>
+        <v>-9.16</v>
       </c>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="18" t="n">
-        <v>15000</v>
+        <v>-6.37</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>15000</v>
+        <v>35.44</v>
       </c>
       <c r="I100" s="18" t="n">
-        <v>35000</v>
+        <v>-22.2</v>
       </c>
       <c r="J100" s="18" t="n">
-        <v>16000</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="K100" s="34" t="n">
-        <v>81000</v>
+        <v>-65.56</v>
       </c>
       <c r="L100" s="18" t="n">
-        <v>31000</v>
+        <v>-45.8</v>
       </c>
       <c r="M100" s="18" t="n">
-        <v>30100</v>
+        <v>-55.2</v>
       </c>
       <c r="N100" s="18" t="n">
-        <v>15300</v>
+        <v>-76.29000000000001</v>
       </c>
       <c r="O100" s="18" t="n">
-        <v>22600</v>
+        <v>3.68</v>
       </c>
       <c r="P100" s="34" t="n">
-        <v>99000</v>
+        <v>-173.61</v>
       </c>
       <c r="Q100" s="18" t="n">
-        <v>1200</v>
+        <v>-156.07</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>101800</v>
+        <v>24.98</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>20000</v>
+        <v>-716.99</v>
       </c>
       <c r="T100" s="18" t="n">
-        <v>28000</v>
+        <v>-310.5</v>
       </c>
       <c r="U100" s="34" t="n">
-        <v>151000</v>
+        <v>-1158.58</v>
       </c>
       <c r="V100" s="18" t="n">
-        <v>0</v>
+        <v>-325.24</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>30000</v>
+        <v>-585.8099999999999</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>50000</v>
+        <v>-0.27</v>
       </c>
       <c r="Z100" s="34" t="n">
-        <v>80000</v>
+        <v>-912.16</v>
+      </c>
+      <c r="AA100" s="18" t="n">
+        <v>-1606.38</v>
       </c>
       <c r="AB100" s="5" t="n"/>
       <c r="AC100" s="10" t="n"/>
@@ -24563,77 +24532,79 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E101" s="18" t="n">
-        <v>357.74</v>
+        <v>-2787.46</v>
       </c>
       <c r="F101" s="9" t="n"/>
       <c r="G101" s="18" t="n">
-        <v>450.71</v>
+        <v>1640.88</v>
       </c>
       <c r="H101" s="18" t="n">
-        <v>491.94</v>
+        <v>-4083.5</v>
       </c>
       <c r="I101" s="18" t="n">
-        <v>458.7</v>
+        <v>-38917.21</v>
       </c>
       <c r="J101" s="18" t="n">
-        <v>485.05</v>
+        <v>-16511.7</v>
       </c>
       <c r="K101" s="34" t="n">
-        <v>1886.4</v>
+        <v>-57871.53</v>
       </c>
       <c r="L101" s="18" t="n">
-        <v>488.81</v>
+        <v>-3086.88</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>517.48</v>
+        <v>-11699.19</v>
       </c>
       <c r="N101" s="18" t="n">
-        <v>527.59</v>
+        <v>-9012.129999999999</v>
       </c>
       <c r="O101" s="18" t="n">
-        <v>552.9299999999999</v>
+        <v>-6481.14</v>
       </c>
       <c r="P101" s="34" t="n">
-        <v>2086.81</v>
+        <v>-30279.34</v>
       </c>
       <c r="Q101" s="18" t="n">
-        <v>530.71</v>
+        <v>31045.05</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>570.05</v>
+        <v>-22379.04</v>
       </c>
       <c r="S101" s="18" t="n">
-        <v>639.6799999999999</v>
+        <v>-8850.68</v>
       </c>
       <c r="T101" s="18" t="n">
-        <v>454.41</v>
+        <v>-4129.06</v>
       </c>
       <c r="U101" s="34" t="n">
-        <v>2194.85</v>
+        <v>-4313.73</v>
       </c>
       <c r="V101" s="18" t="n">
-        <v>592.96</v>
+        <v>-65613.69</v>
       </c>
       <c r="W101" s="18" t="n">
-        <v>582.04</v>
+        <v>-78391.57000000001</v>
       </c>
       <c r="X101" s="18" t="n">
-        <v>541.2</v>
+        <v>-20306.37</v>
       </c>
       <c r="Y101" s="18" t="n">
-        <v>548.96</v>
+        <v>3191.67</v>
       </c>
       <c r="Z101" s="34" t="n">
-        <v>2265.16</v>
+        <v>-161119.96</v>
       </c>
       <c r="AA101" s="18" t="n">
-        <v>588.55</v>
-      </c>
-      <c r="AB101" s="5" t="n"/>
+        <v>-278449.16</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>-31131.53</v>
+      </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
       <c r="AE101" s="11" t="n"/>
@@ -24654,63 +24625,46 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-12017.86</v>
+        <v>0</v>
       </c>
       <c r="F102" s="9" t="n"/>
-      <c r="G102" s="18" t="n">
-        <v>10045.32</v>
-      </c>
-      <c r="H102" s="18" t="n">
-        <v>-9495.870000000001</v>
-      </c>
       <c r="I102" s="18" t="n">
-        <v>37153.75</v>
+        <v>0</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-36729.59</v>
-      </c>
-      <c r="K102" s="34" t="n">
-        <v>973.61</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K102" s="9" t="n"/>
       <c r="L102" s="18" t="n">
-        <v>11812.3</v>
+        <v>49.22</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-33287.89</v>
+        <v>15.92</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>14773.49</v>
+        <v>101.1</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>54974.79</v>
+        <v>46.15</v>
       </c>
       <c r="P102" s="34" t="n">
-        <v>48272.69</v>
-      </c>
-      <c r="Q102" s="18" t="n">
-        <v>103952.23</v>
-      </c>
-      <c r="R102" s="18" t="n">
-        <v>-108299.19</v>
-      </c>
-      <c r="S102" s="18" t="n">
-        <v>-18375.97</v>
+        <v>212.39</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>1.89</v>
       </c>
       <c r="U102" s="9" t="n"/>
-      <c r="V102" s="18" t="n">
-        <v>-9806.389999999999</v>
-      </c>
-      <c r="W102" s="18" t="n">
-        <v>80316.09</v>
-      </c>
-      <c r="X102" s="18" t="n">
-        <v>15136.95</v>
+      <c r="Y102" s="18" t="n">
+        <v>141.01</v>
       </c>
       <c r="Z102" s="9" t="n"/>
+      <c r="AA102" s="18" t="n">
+        <v>1.82</v>
+      </c>
       <c r="AB102" s="5" t="n"/>
       <c r="AC102" s="10" t="n"/>
       <c r="AD102" s="10" t="n"/>
@@ -24732,61 +24686,18 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E103" s="18" t="n">
-        <v>-12017.86</v>
+        <v>178.02</v>
       </c>
       <c r="F103" s="9" t="n"/>
-      <c r="G103" s="18" t="n">
-        <v>63630.95</v>
-      </c>
-      <c r="H103" s="18" t="n">
-        <v>-9495.870000000001</v>
-      </c>
-      <c r="I103" s="18" t="n">
-        <v>37153.75</v>
-      </c>
-      <c r="J103" s="18" t="n">
-        <v>-36729.58</v>
-      </c>
-      <c r="K103" s="34" t="n">
-        <v>54559.25</v>
-      </c>
-      <c r="L103" s="18" t="n">
-        <v>66371.55</v>
-      </c>
-      <c r="M103" s="18" t="n">
-        <v>-33287.89</v>
-      </c>
-      <c r="N103" s="18" t="n">
-        <v>14773.49</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>54974.79</v>
-      </c>
-      <c r="P103" s="34" t="n">
-        <v>102831.94</v>
-      </c>
-      <c r="Q103" s="18" t="n">
-        <v>206784.17</v>
-      </c>
-      <c r="R103" s="18" t="n">
-        <v>-108299.2</v>
-      </c>
-      <c r="S103" s="18" t="n">
-        <v>-18375.97</v>
-      </c>
+      <c r="K103" s="9" t="n"/>
+      <c r="P103" s="9" t="n"/>
       <c r="U103" s="9" t="n"/>
-      <c r="V103" s="18" t="n">
-        <v>123194.8</v>
-      </c>
-      <c r="W103" s="18" t="n">
-        <v>80316.09</v>
-      </c>
       <c r="X103" s="18" t="n">
-        <v>15136.95</v>
+        <v>140.31</v>
       </c>
       <c r="Z103" s="9" t="n"/>
       <c r="AB103" s="5" t="n"/>
@@ -24810,57 +24721,76 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>2782.22</v>
       </c>
       <c r="F104" s="9" t="n"/>
+      <c r="G104" s="18" t="n">
+        <v>1548.89</v>
+      </c>
+      <c r="H104" s="18" t="n">
+        <v>1999.2</v>
+      </c>
       <c r="I104" s="18" t="n">
-        <v>3514.2</v>
+        <v>2895.45</v>
       </c>
       <c r="J104" s="18" t="n">
-        <v>4013.93</v>
-      </c>
-      <c r="K104" s="9" t="n"/>
+        <v>2405.48</v>
+      </c>
+      <c r="K104" s="34" t="n">
+        <v>8849.02</v>
+      </c>
       <c r="L104" s="18" t="n">
-        <v>4013.94</v>
+        <v>4536.04</v>
       </c>
       <c r="M104" s="18" t="n">
-        <v>51013.93</v>
+        <v>11065.58</v>
       </c>
       <c r="N104" s="18" t="n">
-        <v>1013.94</v>
+        <v>9036.9</v>
       </c>
       <c r="O104" s="18" t="n">
-        <v>1013.94</v>
+        <v>6425.72</v>
       </c>
       <c r="P104" s="34" t="n">
-        <v>57055.75</v>
+        <v>31064.24</v>
       </c>
       <c r="Q104" s="18" t="n">
-        <v>1013.94</v>
+        <v>6737.19</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>16305.74</v>
+        <v>15981.3</v>
       </c>
       <c r="S104" s="18" t="n">
-        <v>0</v>
+        <v>20599.22</v>
       </c>
       <c r="T104" s="18" t="n">
-        <v>0</v>
+        <v>7686.07</v>
       </c>
       <c r="U104" s="34" t="n">
-        <v>17319.68</v>
+        <v>51003.78</v>
       </c>
       <c r="V104" s="18" t="n">
-        <v>0</v>
+        <v>5356.11</v>
       </c>
       <c r="W104" s="18" t="n">
-        <v>0</v>
+        <v>3434.1</v>
       </c>
       <c r="X104" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z104" s="9" t="n"/>
+        <v>9098.16</v>
+      </c>
+      <c r="Y104" s="18" t="n">
+        <v>15401.44</v>
+      </c>
+      <c r="Z104" s="34" t="n">
+        <v>33289.81</v>
+      </c>
+      <c r="AA104" s="18" t="n">
+        <v>23598.89</v>
+      </c>
       <c r="AB104" s="5" t="n"/>
       <c r="AC104" s="10" t="n"/>
       <c r="AD104" s="10" t="n"/>
@@ -24882,29 +24812,76 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>2916.22</v>
       </c>
       <c r="F105" s="9" t="n"/>
+      <c r="G105" s="18" t="n">
+        <v>1562.89</v>
+      </c>
+      <c r="H105" s="18" t="n">
+        <v>2129</v>
+      </c>
+      <c r="I105" s="18" t="n">
+        <v>3193.3</v>
+      </c>
       <c r="J105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="9" t="n"/>
+        <v>2601.36</v>
+      </c>
+      <c r="K105" s="34" t="n">
+        <v>9486.549999999999</v>
+      </c>
+      <c r="L105" s="18" t="n">
+        <v>4539.04</v>
+      </c>
+      <c r="M105" s="18" t="n">
+        <v>11062.58</v>
+      </c>
+      <c r="N105" s="18" t="n">
+        <v>9036.9</v>
+      </c>
       <c r="O105" s="18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P105" s="9" t="n"/>
+        <v>6765.8</v>
+      </c>
+      <c r="P105" s="34" t="n">
+        <v>31404.32</v>
+      </c>
+      <c r="Q105" s="18" t="n">
+        <v>6737.19</v>
+      </c>
+      <c r="R105" s="18" t="n">
+        <v>16105.91</v>
+      </c>
+      <c r="S105" s="18" t="n">
+        <v>21435.41</v>
+      </c>
       <c r="T105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" s="9" t="n"/>
+        <v>10223.38</v>
+      </c>
+      <c r="U105" s="34" t="n">
+        <v>54501.89</v>
+      </c>
+      <c r="V105" s="18" t="n">
+        <v>6838.01</v>
+      </c>
+      <c r="W105" s="18" t="n">
+        <v>4076.3</v>
+      </c>
       <c r="X105" s="18" t="n">
-        <v>0</v>
+        <v>9986.15</v>
       </c>
       <c r="Y105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z105" s="9" t="n"/>
+        <v>17961.31</v>
+      </c>
+      <c r="Z105" s="34" t="n">
+        <v>38861.77</v>
+      </c>
+      <c r="AA105" s="18" t="n">
+        <v>24939.45</v>
+      </c>
       <c r="AB105" s="5" t="n"/>
       <c r="AC105" s="10" t="n"/>
       <c r="AD105" s="10" t="n"/>
@@ -24926,17 +24903,57 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>134</v>
       </c>
       <c r="F106" s="9" t="n"/>
+      <c r="G106" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="H106" s="18" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>297.85</v>
+      </c>
       <c r="J106" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="9" t="n"/>
+        <v>195.88</v>
+      </c>
+      <c r="K106" s="34" t="n">
+        <v>637.53</v>
+      </c>
+      <c r="L106" s="18" t="n">
+        <v>3</v>
+      </c>
       <c r="P106" s="9" t="n"/>
+      <c r="S106" s="18" t="n">
+        <v>836.1900000000001</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>2537.31</v>
+      </c>
       <c r="U106" s="9" t="n"/>
-      <c r="Z106" s="9" t="n"/>
+      <c r="V106" s="18" t="n">
+        <v>1481.9</v>
+      </c>
+      <c r="W106" s="18" t="n">
+        <v>642.2</v>
+      </c>
+      <c r="X106" s="18" t="n">
+        <v>887.99</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>2559.87</v>
+      </c>
+      <c r="Z106" s="34" t="n">
+        <v>5571.96</v>
+      </c>
+      <c r="AA106" s="18" t="n">
+        <v>1340.56</v>
+      </c>
       <c r="AB106" s="5" t="n"/>
       <c r="AC106" s="10" t="n"/>
       <c r="AD106" s="10" t="n"/>
@@ -24958,21 +24975,79 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>사채의증가</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>724.25</v>
       </c>
       <c r="F107" s="9" t="n"/>
-      <c r="K107" s="9" t="n"/>
+      <c r="G107" s="18" t="n">
+        <v>10235.29</v>
+      </c>
+      <c r="H107" s="18" t="n">
+        <v>8981.059999999999</v>
+      </c>
+      <c r="I107" s="18" t="n">
+        <v>65245.88</v>
+      </c>
+      <c r="J107" s="18" t="n">
+        <v>-4507.88</v>
+      </c>
+      <c r="K107" s="34" t="n">
+        <v>79954.35000000001</v>
+      </c>
+      <c r="L107" s="18" t="n">
+        <v>-4502.75</v>
+      </c>
+      <c r="M107" s="18" t="n">
+        <v>7267.09</v>
+      </c>
       <c r="N107" s="18" t="n">
-        <v>0</v>
+        <v>24158.47</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" s="9" t="n"/>
-      <c r="U107" s="9" t="n"/>
-      <c r="Z107" s="9" t="n"/>
-      <c r="AB107" s="5" t="n"/>
+        <v>-18166.87</v>
+      </c>
+      <c r="P107" s="34" t="n">
+        <v>8755.940000000001</v>
+      </c>
+      <c r="Q107" s="18" t="n">
+        <v>86685.44</v>
+      </c>
+      <c r="R107" s="18" t="n">
+        <v>-122797.81</v>
+      </c>
+      <c r="S107" s="18" t="n">
+        <v>-4727.67</v>
+      </c>
+      <c r="T107" s="18" t="n">
+        <v>-16454.41</v>
+      </c>
+      <c r="U107" s="34" t="n">
+        <v>-57294.45</v>
+      </c>
+      <c r="V107" s="18" t="n">
+        <v>9407.040000000001</v>
+      </c>
+      <c r="W107" s="18" t="n">
+        <v>-10582.04</v>
+      </c>
+      <c r="X107" s="18" t="n">
+        <v>-541.2</v>
+      </c>
+      <c r="Y107" s="18" t="n">
+        <v>-20548.96</v>
+      </c>
+      <c r="Z107" s="34" t="n">
+        <v>-22265.16</v>
+      </c>
+      <c r="AA107" s="18" t="n">
+        <v>-968</v>
+      </c>
+      <c r="AB107" s="19" t="n">
+        <v>-41153.13</v>
+      </c>
       <c r="AC107" s="10" t="n"/>
       <c r="AD107" s="10" t="n"/>
       <c r="AE107" s="11" t="n"/>
@@ -24993,48 +25068,54 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>35000</v>
       </c>
       <c r="F108" s="9" t="n"/>
-      <c r="K108" s="9" t="n"/>
+      <c r="G108" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J108" s="18" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K108" s="34" t="n">
+        <v>81000</v>
+      </c>
+      <c r="L108" s="18" t="n">
+        <v>31000</v>
+      </c>
+      <c r="M108" s="18" t="n">
+        <v>49000</v>
+      </c>
+      <c r="N108" s="18" t="n">
+        <v>41000</v>
+      </c>
       <c r="O108" s="18" t="n">
-        <v>563.78</v>
-      </c>
-      <c r="P108" s="9" t="n"/>
-      <c r="Q108" s="18" t="n">
-        <v>907.79</v>
-      </c>
-      <c r="R108" s="18" t="n">
-        <v>991.61</v>
-      </c>
-      <c r="S108" s="18" t="n">
-        <v>1237.84</v>
+        <v>6000</v>
+      </c>
+      <c r="P108" s="34" t="n">
+        <v>127000</v>
       </c>
       <c r="T108" s="18" t="n">
-        <v>860.65</v>
-      </c>
-      <c r="U108" s="34" t="n">
-        <v>3997.89</v>
-      </c>
-      <c r="V108" s="18" t="n">
-        <v>1067.81</v>
-      </c>
-      <c r="W108" s="18" t="n">
-        <v>2191.27</v>
-      </c>
+        <v>22000</v>
+      </c>
+      <c r="U108" s="9" t="n"/>
       <c r="X108" s="18" t="n">
-        <v>3414.54</v>
+        <v>0</v>
       </c>
       <c r="Y108" s="18" t="n">
-        <v>3346.48</v>
-      </c>
-      <c r="Z108" s="34" t="n">
-        <v>10020.1</v>
-      </c>
-      <c r="AA108" s="18" t="n">
-        <v>3251.68</v>
-      </c>
+        <v>30000</v>
+      </c>
+      <c r="Z108" s="9" t="n"/>
       <c r="AB108" s="5" t="n"/>
       <c r="AC108" s="10" t="n"/>
       <c r="AD108" s="10" t="n"/>
@@ -25056,47 +25137,47 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>1082</v>
       </c>
       <c r="F109" s="9" t="n"/>
-      <c r="K109" s="9" t="n"/>
-      <c r="O109" s="18" t="n">
-        <v>-3143.38</v>
+      <c r="G109" s="18" t="n">
+        <v>686</v>
+      </c>
+      <c r="H109" s="18" t="n">
+        <v>473</v>
+      </c>
+      <c r="I109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="34" t="n">
+        <v>1159</v>
       </c>
       <c r="P109" s="9" t="n"/>
-      <c r="Q109" s="18" t="n">
-        <v>-2978.78</v>
-      </c>
-      <c r="R109" s="18" t="n">
-        <v>-1961.83</v>
-      </c>
-      <c r="S109" s="18" t="n">
-        <v>-1193.58</v>
-      </c>
       <c r="T109" s="18" t="n">
-        <v>-976.73</v>
-      </c>
-      <c r="U109" s="34" t="n">
-        <v>-7110.92</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U109" s="9" t="n"/>
       <c r="V109" s="18" t="n">
-        <v>-698.3099999999999</v>
+        <v>10000</v>
       </c>
       <c r="W109" s="18" t="n">
-        <v>-662.1799999999999</v>
+        <v>0</v>
       </c>
       <c r="X109" s="18" t="n">
-        <v>-563.53</v>
+        <v>0</v>
       </c>
       <c r="Y109" s="18" t="n">
-        <v>-627.0599999999999</v>
+        <v>0</v>
       </c>
       <c r="Z109" s="34" t="n">
-        <v>-2551.08</v>
-      </c>
-      <c r="AA109" s="18" t="n">
-        <v>-379.45</v>
+        <v>10000</v>
       </c>
       <c r="AB109" s="5" t="n"/>
       <c r="AC109" s="10" t="n"/>
@@ -25119,23 +25200,73 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="n">
+        <v>35000</v>
       </c>
       <c r="F110" s="9" t="n"/>
-      <c r="K110" s="9" t="n"/>
-      <c r="P110" s="9" t="n"/>
+      <c r="G110" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I110" s="18" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J110" s="18" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K110" s="34" t="n">
+        <v>81000</v>
+      </c>
+      <c r="L110" s="18" t="n">
+        <v>31000</v>
+      </c>
+      <c r="M110" s="18" t="n">
+        <v>30100</v>
+      </c>
+      <c r="N110" s="18" t="n">
+        <v>15300</v>
+      </c>
+      <c r="O110" s="18" t="n">
+        <v>22600</v>
+      </c>
+      <c r="P110" s="34" t="n">
+        <v>99000</v>
+      </c>
+      <c r="Q110" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R110" s="18" t="n">
+        <v>101800</v>
+      </c>
       <c r="S110" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T110" s="18" t="n">
+        <v>28000</v>
+      </c>
+      <c r="U110" s="34" t="n">
+        <v>151000</v>
+      </c>
+      <c r="V110" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T110" s="18" t="n">
-        <v>10000</v>
-      </c>
-      <c r="U110" s="9" t="n"/>
+      <c r="W110" s="18" t="n">
+        <v>30000</v>
+      </c>
       <c r="X110" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n"/>
+      <c r="Y110" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="Z110" s="34" t="n">
+        <v>80000</v>
+      </c>
       <c r="AB110" s="5" t="n"/>
       <c r="AC110" s="10" t="n"/>
       <c r="AD110" s="10" t="n"/>
@@ -25150,6 +25281,600 @@
       <c r="AM110" s="10" t="n"/>
       <c r="AN110" s="10" t="n"/>
       <c r="AO110" s="11" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="F111" s="9" t="n"/>
+      <c r="G111" s="18" t="n">
+        <v>450.71</v>
+      </c>
+      <c r="H111" s="18" t="n">
+        <v>491.94</v>
+      </c>
+      <c r="I111" s="18" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="J111" s="18" t="n">
+        <v>485.05</v>
+      </c>
+      <c r="K111" s="34" t="n">
+        <v>1886.4</v>
+      </c>
+      <c r="L111" s="18" t="n">
+        <v>488.81</v>
+      </c>
+      <c r="M111" s="18" t="n">
+        <v>517.48</v>
+      </c>
+      <c r="N111" s="18" t="n">
+        <v>527.59</v>
+      </c>
+      <c r="O111" s="18" t="n">
+        <v>552.9299999999999</v>
+      </c>
+      <c r="P111" s="34" t="n">
+        <v>2086.81</v>
+      </c>
+      <c r="Q111" s="18" t="n">
+        <v>530.71</v>
+      </c>
+      <c r="R111" s="18" t="n">
+        <v>570.05</v>
+      </c>
+      <c r="S111" s="18" t="n">
+        <v>639.6799999999999</v>
+      </c>
+      <c r="T111" s="18" t="n">
+        <v>454.41</v>
+      </c>
+      <c r="U111" s="34" t="n">
+        <v>2194.85</v>
+      </c>
+      <c r="V111" s="18" t="n">
+        <v>592.96</v>
+      </c>
+      <c r="W111" s="18" t="n">
+        <v>582.04</v>
+      </c>
+      <c r="X111" s="18" t="n">
+        <v>541.2</v>
+      </c>
+      <c r="Y111" s="18" t="n">
+        <v>548.96</v>
+      </c>
+      <c r="Z111" s="34" t="n">
+        <v>2265.16</v>
+      </c>
+      <c r="AA111" s="18" t="n">
+        <v>588.55</v>
+      </c>
+      <c r="AB111" s="5" t="n"/>
+      <c r="AC111" s="10" t="n"/>
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="10" t="n"/>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="11" t="n"/>
+      <c r="AK111" s="10" t="n"/>
+      <c r="AL111" s="10" t="n"/>
+      <c r="AM111" s="10" t="n"/>
+      <c r="AN111" s="10" t="n"/>
+      <c r="AO111" s="11" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="n">
+        <v>-12017.86</v>
+      </c>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="18" t="n">
+        <v>10045.32</v>
+      </c>
+      <c r="H112" s="18" t="n">
+        <v>-9495.870000000001</v>
+      </c>
+      <c r="I112" s="18" t="n">
+        <v>37153.75</v>
+      </c>
+      <c r="J112" s="18" t="n">
+        <v>-36729.59</v>
+      </c>
+      <c r="K112" s="34" t="n">
+        <v>973.61</v>
+      </c>
+      <c r="L112" s="18" t="n">
+        <v>11812.3</v>
+      </c>
+      <c r="M112" s="18" t="n">
+        <v>-33287.89</v>
+      </c>
+      <c r="N112" s="18" t="n">
+        <v>14773.49</v>
+      </c>
+      <c r="O112" s="18" t="n">
+        <v>54974.79</v>
+      </c>
+      <c r="P112" s="34" t="n">
+        <v>48272.69</v>
+      </c>
+      <c r="Q112" s="18" t="n">
+        <v>103952.23</v>
+      </c>
+      <c r="R112" s="18" t="n">
+        <v>-108299.19</v>
+      </c>
+      <c r="S112" s="18" t="n">
+        <v>-18375.97</v>
+      </c>
+      <c r="U112" s="9" t="n"/>
+      <c r="V112" s="18" t="n">
+        <v>-9806.389999999999</v>
+      </c>
+      <c r="W112" s="18" t="n">
+        <v>80316.09</v>
+      </c>
+      <c r="X112" s="18" t="n">
+        <v>15136.95</v>
+      </c>
+      <c r="Z112" s="9" t="n"/>
+      <c r="AB112" s="5" t="n"/>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="11" t="n"/>
+      <c r="AK112" s="10" t="n"/>
+      <c r="AL112" s="10" t="n"/>
+      <c r="AM112" s="10" t="n"/>
+      <c r="AN112" s="10" t="n"/>
+      <c r="AO112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>-12017.86</v>
+      </c>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="18" t="n">
+        <v>63630.95</v>
+      </c>
+      <c r="H113" s="18" t="n">
+        <v>-9495.870000000001</v>
+      </c>
+      <c r="I113" s="18" t="n">
+        <v>37153.75</v>
+      </c>
+      <c r="J113" s="18" t="n">
+        <v>-36729.58</v>
+      </c>
+      <c r="K113" s="34" t="n">
+        <v>54559.25</v>
+      </c>
+      <c r="L113" s="18" t="n">
+        <v>66371.55</v>
+      </c>
+      <c r="M113" s="18" t="n">
+        <v>-33287.89</v>
+      </c>
+      <c r="N113" s="18" t="n">
+        <v>14773.49</v>
+      </c>
+      <c r="O113" s="18" t="n">
+        <v>54974.79</v>
+      </c>
+      <c r="P113" s="34" t="n">
+        <v>102831.94</v>
+      </c>
+      <c r="Q113" s="18" t="n">
+        <v>206784.17</v>
+      </c>
+      <c r="R113" s="18" t="n">
+        <v>-108299.2</v>
+      </c>
+      <c r="S113" s="18" t="n">
+        <v>-18375.97</v>
+      </c>
+      <c r="U113" s="9" t="n"/>
+      <c r="V113" s="18" t="n">
+        <v>123194.8</v>
+      </c>
+      <c r="W113" s="18" t="n">
+        <v>80316.09</v>
+      </c>
+      <c r="X113" s="18" t="n">
+        <v>15136.95</v>
+      </c>
+      <c r="Z113" s="9" t="n"/>
+      <c r="AB113" s="5" t="n"/>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="11" t="n"/>
+      <c r="AK113" s="10" t="n"/>
+      <c r="AL113" s="10" t="n"/>
+      <c r="AM113" s="10" t="n"/>
+      <c r="AN113" s="10" t="n"/>
+      <c r="AO113" s="11" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="n"/>
+      <c r="I114" s="18" t="n">
+        <v>3514.2</v>
+      </c>
+      <c r="J114" s="18" t="n">
+        <v>4013.93</v>
+      </c>
+      <c r="K114" s="9" t="n"/>
+      <c r="L114" s="18" t="n">
+        <v>4013.94</v>
+      </c>
+      <c r="M114" s="18" t="n">
+        <v>51013.93</v>
+      </c>
+      <c r="N114" s="18" t="n">
+        <v>1013.94</v>
+      </c>
+      <c r="O114" s="18" t="n">
+        <v>1013.94</v>
+      </c>
+      <c r="P114" s="34" t="n">
+        <v>57055.75</v>
+      </c>
+      <c r="Q114" s="18" t="n">
+        <v>1013.94</v>
+      </c>
+      <c r="R114" s="18" t="n">
+        <v>16305.74</v>
+      </c>
+      <c r="S114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="34" t="n">
+        <v>17319.68</v>
+      </c>
+      <c r="V114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="9" t="n"/>
+      <c r="AB114" s="5" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="11" t="n"/>
+      <c r="AK114" s="10" t="n"/>
+      <c r="AL114" s="10" t="n"/>
+      <c r="AM114" s="10" t="n"/>
+      <c r="AN114" s="10" t="n"/>
+      <c r="AO114" s="11" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="n"/>
+      <c r="J115" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="9" t="n"/>
+      <c r="O115" s="18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P115" s="9" t="n"/>
+      <c r="T115" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="9" t="n"/>
+      <c r="X115" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="9" t="n"/>
+      <c r="AB115" s="5" t="n"/>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="11" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="11" t="n"/>
+      <c r="AK115" s="10" t="n"/>
+      <c r="AL115" s="10" t="n"/>
+      <c r="AM115" s="10" t="n"/>
+      <c r="AN115" s="10" t="n"/>
+      <c r="AO115" s="11" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="n"/>
+      <c r="J116" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="9" t="n"/>
+      <c r="P116" s="9" t="n"/>
+      <c r="U116" s="9" t="n"/>
+      <c r="Z116" s="9" t="n"/>
+      <c r="AB116" s="5" t="n"/>
+      <c r="AC116" s="10" t="n"/>
+      <c r="AD116" s="10" t="n"/>
+      <c r="AE116" s="11" t="n"/>
+      <c r="AF116" s="10" t="n"/>
+      <c r="AG116" s="10" t="n"/>
+      <c r="AH116" s="10" t="n"/>
+      <c r="AI116" s="10" t="n"/>
+      <c r="AJ116" s="11" t="n"/>
+      <c r="AK116" s="10" t="n"/>
+      <c r="AL116" s="10" t="n"/>
+      <c r="AM116" s="10" t="n"/>
+      <c r="AN116" s="10" t="n"/>
+      <c r="AO116" s="11" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>사채의증가</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="n"/>
+      <c r="K117" s="9" t="n"/>
+      <c r="N117" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="9" t="n"/>
+      <c r="U117" s="9" t="n"/>
+      <c r="Z117" s="9" t="n"/>
+      <c r="AB117" s="5" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="11" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="11" t="n"/>
+      <c r="AK117" s="10" t="n"/>
+      <c r="AL117" s="10" t="n"/>
+      <c r="AM117" s="10" t="n"/>
+      <c r="AN117" s="10" t="n"/>
+      <c r="AO117" s="11" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="n"/>
+      <c r="K118" s="9" t="n"/>
+      <c r="O118" s="18" t="n">
+        <v>563.78</v>
+      </c>
+      <c r="P118" s="9" t="n"/>
+      <c r="Q118" s="18" t="n">
+        <v>907.79</v>
+      </c>
+      <c r="R118" s="18" t="n">
+        <v>991.61</v>
+      </c>
+      <c r="S118" s="18" t="n">
+        <v>1237.84</v>
+      </c>
+      <c r="T118" s="18" t="n">
+        <v>860.65</v>
+      </c>
+      <c r="U118" s="34" t="n">
+        <v>3997.89</v>
+      </c>
+      <c r="V118" s="18" t="n">
+        <v>1067.81</v>
+      </c>
+      <c r="W118" s="18" t="n">
+        <v>2191.27</v>
+      </c>
+      <c r="X118" s="18" t="n">
+        <v>3414.54</v>
+      </c>
+      <c r="Y118" s="18" t="n">
+        <v>3346.48</v>
+      </c>
+      <c r="Z118" s="34" t="n">
+        <v>10020.1</v>
+      </c>
+      <c r="AA118" s="18" t="n">
+        <v>3251.68</v>
+      </c>
+      <c r="AB118" s="5" t="n"/>
+      <c r="AC118" s="10" t="n"/>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="11" t="n"/>
+      <c r="AF118" s="10" t="n"/>
+      <c r="AG118" s="10" t="n"/>
+      <c r="AH118" s="10" t="n"/>
+      <c r="AI118" s="10" t="n"/>
+      <c r="AJ118" s="11" t="n"/>
+      <c r="AK118" s="10" t="n"/>
+      <c r="AL118" s="10" t="n"/>
+      <c r="AM118" s="10" t="n"/>
+      <c r="AN118" s="10" t="n"/>
+      <c r="AO118" s="11" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n"/>
+      <c r="K119" s="9" t="n"/>
+      <c r="O119" s="18" t="n">
+        <v>-3143.38</v>
+      </c>
+      <c r="P119" s="9" t="n"/>
+      <c r="Q119" s="18" t="n">
+        <v>-2978.78</v>
+      </c>
+      <c r="R119" s="18" t="n">
+        <v>-1961.83</v>
+      </c>
+      <c r="S119" s="18" t="n">
+        <v>-1193.58</v>
+      </c>
+      <c r="T119" s="18" t="n">
+        <v>-976.73</v>
+      </c>
+      <c r="U119" s="34" t="n">
+        <v>-7110.92</v>
+      </c>
+      <c r="V119" s="18" t="n">
+        <v>-698.3099999999999</v>
+      </c>
+      <c r="W119" s="18" t="n">
+        <v>-662.1799999999999</v>
+      </c>
+      <c r="X119" s="18" t="n">
+        <v>-563.53</v>
+      </c>
+      <c r="Y119" s="18" t="n">
+        <v>-627.0599999999999</v>
+      </c>
+      <c r="Z119" s="34" t="n">
+        <v>-2551.08</v>
+      </c>
+      <c r="AA119" s="18" t="n">
+        <v>-379.45</v>
+      </c>
+      <c r="AB119" s="5" t="n"/>
+      <c r="AC119" s="10" t="n"/>
+      <c r="AD119" s="10" t="n"/>
+      <c r="AE119" s="11" t="n"/>
+      <c r="AF119" s="10" t="n"/>
+      <c r="AG119" s="10" t="n"/>
+      <c r="AH119" s="10" t="n"/>
+      <c r="AI119" s="10" t="n"/>
+      <c r="AJ119" s="11" t="n"/>
+      <c r="AK119" s="10" t="n"/>
+      <c r="AL119" s="10" t="n"/>
+      <c r="AM119" s="10" t="n"/>
+      <c r="AN119" s="10" t="n"/>
+      <c r="AO119" s="11" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="n"/>
+      <c r="K120" s="9" t="n"/>
+      <c r="P120" s="9" t="n"/>
+      <c r="S120" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="U120" s="9" t="n"/>
+      <c r="X120" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" s="9" t="n"/>
+      <c r="AB120" s="5" t="n"/>
+      <c r="AC120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="11" t="n"/>
+      <c r="AF120" s="10" t="n"/>
+      <c r="AG120" s="10" t="n"/>
+      <c r="AH120" s="10" t="n"/>
+      <c r="AI120" s="10" t="n"/>
+      <c r="AJ120" s="11" t="n"/>
+      <c r="AK120" s="10" t="n"/>
+      <c r="AL120" s="10" t="n"/>
+      <c r="AM120" s="10" t="n"/>
+      <c r="AN120" s="10" t="n"/>
+      <c r="AO120" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -38334,7 +39059,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1881.1</v>
+        <v>1882.4</v>
       </c>
     </row>
     <row r="30">
@@ -38354,7 +39079,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.93</v>
+        <v>24.92</v>
       </c>
     </row>
     <row r="32">
@@ -38374,7 +39099,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2415</v>
+        <v>0.2417</v>
       </c>
     </row>
     <row r="34">
@@ -38384,7 +39109,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="35">
@@ -38394,7 +39119,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>20900</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 144323억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 144300억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 151179억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 151129억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 148563억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 148487억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152580억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152479억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 158222억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 158118억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163957억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163857억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163944억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163847억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 144323억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 144300억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 151179억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 151129억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 148563억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 148487억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152580억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152479억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 158222억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 158118억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163957억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163857억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163944억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163847억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2166,19 +2166,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5432억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5431억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5815억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5814억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6185억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6184억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2226,19 +2226,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5432억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5431억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5815억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5814억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6185억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6184억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>48600</v>
+        <v>47500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6455,7 +6455,7 @@
         <v>35800</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>47850</v>
+        <v>46650</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>48750</v>
+        <v>48333.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6708,26 +6708,26 @@
         <v>0.212830794</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.265932656</v>
+        <v>0.26572836</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.283906235</v>
+        <v>0.283484841</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.146033604</v>
+        <v>0.145450494</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.106420327</v>
+        <v>0.105689523</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.096300044</v>
+        <v>0.095761573</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.084524895</v>
+        <v>0.084215269</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.103534936</v>
+        <v>0.103444013</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.088338902</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.088340101</v>
+        <v>0.08833909199999999</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088341214</v>
+        <v>0.08834078300000001</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08833978100000001</v>
+        <v>0.0883393</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088340237</v>
+        <v>0.08834030599999999</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.08834025600000001</v>
+        <v>0.088340207</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08833946600000001</v>
+        <v>0.08833940699999999</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088339374</v>
+        <v>0.08834055</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.005193685</v>
+        <v>0.005531222</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.013745631</v>
+        <v>-0.013358483</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.008668352000000001</v>
+        <v>-0.008222760000000001</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.006423335</v>
+        <v>0.002326137</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.002115309</v>
+        <v>-0.003322117</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.002105781</v>
+        <v>-0.00765872</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.001828773</v>
+        <v>0.005685371</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.006278717</v>
+        <v>-0.005846332</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.003180006</v>
+        <v>-0.004611685</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.0046567</v>
+        <v>0.007076258</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.005193685</v>
+        <v>0.005531222</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.013745631</v>
+        <v>-0.013358483</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.008668352000000001</v>
+        <v>-0.008222760000000001</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.006423335</v>
+        <v>0.002326137</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.002115309</v>
+        <v>-0.003322117</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.002105781</v>
+        <v>-0.00765872</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.001828773</v>
+        <v>0.005685371</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.006278717</v>
+        <v>-0.005846332</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.003180006</v>
+        <v>-0.004611685</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.0046567</v>
+        <v>0.007076258</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8773,26 +8773,26 @@
         <v>0.09326825499999999</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.093434874</v>
+        <v>0.093421221</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.083195777</v>
+        <v>0.083171843</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.09460849</v>
+        <v>0.09456795599999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.07443664899999999</v>
+        <v>0.074395641</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.07511541100000001</v>
+        <v>0.075078566</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.067416775</v>
+        <v>0.067390016</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.07870809300000001</v>
+        <v>0.078676986</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8901,26 +8901,26 @@
         <v>0.084898483</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.085703552</v>
+        <v>0.085691028</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.076855111</v>
+        <v>0.076830622</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.08791262900000001</v>
+        <v>0.087874938</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.069594156</v>
+        <v>0.069557597</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.07054487299999999</v>
+        <v>0.070509799</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.06358836800000001</v>
+        <v>0.063560889</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.074503691</v>
+        <v>0.074475311</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>48600</v>
+        <v>47500</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2199988214933425</v>
+        <v>0.219998777420707</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577678607172731</v>
+        <v>0.04577673492341457</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03769908970863353</v>
+        <v>0.03769997340786517</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05044540736677777</v>
+        <v>0.05044875663658308</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40661,7 +40661,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1514.4</v>
+        <v>1514.3</v>
       </c>
     </row>
     <row r="30">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>32.09</v>
+        <v>31.37</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6.24</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 144300억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 144280억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 151129억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 151078억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 148487억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 148404억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152479억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152365억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 158118억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 157993억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163857억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163735억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163847억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163730억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 144300억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 144280억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 151129억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 151078억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 148487억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 148404억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152479억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152365억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 158118억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 157993억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163857억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163735억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163847억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163730억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2172,13 +2172,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5814억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5813억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6184억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6183억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2232,13 +2232,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5814억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5813억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6184억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6183억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.77% / 부채 5.04% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
+          <t>· 이자율 자산 3.77% / 부채 5.05% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>47500</v>
+        <v>45550</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6455,7 +6455,7 @@
         <v>35800</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>46650</v>
+        <v>45250</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>48333.3</v>
+        <v>47700</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6708,26 +6708,26 @@
         <v>0.212830794</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.26572836</v>
+        <v>0.265551672</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.283484841</v>
+        <v>0.28304601</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.145450494</v>
+        <v>0.144809073</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.105689523</v>
+        <v>0.104860801</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.095761573</v>
+        <v>0.095048516</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.084215269</v>
+        <v>0.08378200199999999</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.103444013</v>
+        <v>0.103274582</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.088338902</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08833909199999999</v>
+        <v>0.08834051800000001</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.08834078300000001</v>
+        <v>0.088339287</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.0883393</v>
+        <v>0.088339679</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08834030599999999</v>
+        <v>0.088339559</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.088340207</v>
+        <v>0.088340349</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08833940699999999</v>
+        <v>0.088340161</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.08834055</v>
+        <v>0.088339316</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.005531222</v>
+        <v>0.00452108</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.013358483</v>
+        <v>-0.014471397</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.008222760000000001</v>
+        <v>-0.009141524999999999</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.002326137</v>
+        <v>0.00245229</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.003322117</v>
+        <v>-0.003632236</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.00765872</v>
+        <v>-0.010073575</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.005685371</v>
+        <v>0.000704066</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.005846332</v>
+        <v>-0.003734469</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.004611685</v>
+        <v>-0.003205396</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.007076258</v>
+        <v>0.004186867</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.005531222</v>
+        <v>0.00452108</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.013358483</v>
+        <v>-0.014471397</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.008222760000000001</v>
+        <v>-0.009141524999999999</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.002326137</v>
+        <v>0.00245229</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.003322117</v>
+        <v>-0.003632236</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.00765872</v>
+        <v>-0.010073575</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.005685371</v>
+        <v>0.000704066</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.005846332</v>
+        <v>-0.003734469</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.004611685</v>
+        <v>-0.003205396</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.007076258</v>
+        <v>0.004186867</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8773,26 +8773,26 @@
         <v>0.09326825499999999</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.093421221</v>
+        <v>0.093410299</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.083171843</v>
+        <v>0.083145203</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.09456795599999999</v>
+        <v>0.09452050400000001</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.074395641</v>
+        <v>0.07435298999999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.075078566</v>
+        <v>0.075032499</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.067390016</v>
+        <v>0.067353412</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.078676986</v>
+        <v>0.078641049</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8901,26 +8901,26 @@
         <v>0.084898483</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.085691028</v>
+        <v>0.085678505</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.076830622</v>
+        <v>0.076810745</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.087874938</v>
+        <v>0.087830441</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.069557597</v>
+        <v>0.06951526199999999</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.070509799</v>
+        <v>0.070466029</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.063560889</v>
+        <v>0.063527505</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.074475311</v>
+        <v>0.074438782</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9583,11 +9583,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>47500</v>
+        <v>45550</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 48,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 48,600원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.219998777420707</v>
+        <v>0.2200003057683193</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577673492341457</v>
+        <v>0.04577653906244564</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03769997340786517</v>
+        <v>0.03770166582027065</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05044875663658308</v>
+        <v>0.05047345992989984</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40661,7 +40661,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1514.3</v>
+        <v>1514.2</v>
       </c>
     </row>
     <row r="30">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.37</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6.1</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 137904억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 137532억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 144280억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 143247억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 151078억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 149993억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 148404억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 148152억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152365억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154441억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 157993억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163998억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163735억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 174482억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163730억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 179790억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 137904억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 137532억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 144280억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 143247억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 151078억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 149993억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 148404억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 148152억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152365억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154441억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 157993억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163998억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163735억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 174482억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163730억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 179790억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2142,43 +2142,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3993억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3992억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4335억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4332억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4668억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4662억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5078억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5072억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5431억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5429억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5813억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5825억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6183억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6216억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2202,43 +2202,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3993억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3992억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4335억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4332억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4668억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4662억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5078억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5072억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5431억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5429억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5813억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5825억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6183억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6216억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.77% / 부채 5.05% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
+          <t>· 이자율 자산 3.77% / 부채 5.04% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -6705,29 +6705,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.212830794</v>
+        <v>0.209566393</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.265551672</v>
+        <v>0.256493638</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.28304601</v>
+        <v>0.273833465</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.144809073</v>
+        <v>0.142861903</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.104860801</v>
+        <v>0.122941162</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.095048516</v>
+        <v>0.144858468</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.08378200199999999</v>
+        <v>0.163268472</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.103274582</v>
+        <v>0.213552144</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7019,32 +7019,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.088338902</v>
+        <v>0.088340238</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08834051800000001</v>
+        <v>0.08834017800000001</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088339287</v>
+        <v>0.088339368</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.088339679</v>
+        <v>0.088340768</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088339559</v>
+        <v>0.088339599</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.088340349</v>
+        <v>0.08833983300000001</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088340161</v>
+        <v>0.088339528</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088339316</v>
+        <v>0.08834075600000001</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.00452108</v>
+        <v>0.004439655</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.014471397</v>
+        <v>-0.015072242</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009141524999999999</v>
+        <v>-0.002242063</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.00245229</v>
+        <v>-0.006601081</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.003632236</v>
+        <v>-0.0016624</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.010073575</v>
+        <v>-0.00051342</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000704066</v>
+        <v>-0.010876311</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.003734469</v>
+        <v>-0.005872552</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.003205396</v>
+        <v>-0.004978206</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.004186867</v>
+        <v>0.000980425</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.00452108</v>
+        <v>0.004439655</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.014471397</v>
+        <v>-0.015072242</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.009141524999999999</v>
+        <v>-0.002242063</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.00245229</v>
+        <v>-0.006601081</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.003632236</v>
+        <v>-0.0016624</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.010073575</v>
+        <v>-0.00051342</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.000704066</v>
+        <v>-0.010876311</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.003734469</v>
+        <v>-0.005872552</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.003205396</v>
+        <v>-0.004978206</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.004186867</v>
+        <v>0.000980425</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8770,29 +8770,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.09326825499999999</v>
+        <v>0.09303839</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.093410299</v>
+        <v>0.092807241</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.083145203</v>
+        <v>0.082658756</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.09452050400000001</v>
+        <v>0.094478083</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.07435298999999999</v>
+        <v>0.07535291</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.075032499</v>
+        <v>0.077631723</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.067353412</v>
+        <v>0.07116739499999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.078641049</v>
+        <v>0.08520251</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8898,29 +8898,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.084898483</v>
+        <v>0.08468653499999999</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.085678505</v>
+        <v>0.08512908900000001</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.076810745</v>
+        <v>0.076354452</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.087830441</v>
+        <v>0.087783493</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.06951526199999999</v>
+        <v>0.07044241900000001</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.070466029</v>
+        <v>0.072907687</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.063527505</v>
+        <v>0.06713100900000001</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.074438782</v>
+        <v>0.080675703</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2200003057683193</v>
+        <v>0.2200021822429607</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577653906244564</v>
+        <v>0.04577676058516068</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03770166582027065</v>
+        <v>0.03769588162953518</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05047345992989984</v>
+        <v>0.05040849687653878</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40661,7 +40661,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1514.2</v>
+        <v>1510.6</v>
       </c>
     </row>
     <row r="30">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.08</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="32">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1944</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 143247억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 143236억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 149993억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 149981억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 148152억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 148139억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 154441억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154428억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163998억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163996억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 174482억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 174480억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 179790억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 179788억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 143247억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 143236억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 149993억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 149981억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 148152억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 148139억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 154441억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154428억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163998억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163996억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 174482억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 174480억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 179790억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 179788억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>45550</v>
+        <v>41350</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6455,7 +6455,7 @@
         <v>35800</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>45250</v>
+        <v>41000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>47700</v>
+        <v>46380</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6708,26 +6708,26 @@
         <v>0.209566393</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.256493638</v>
+        <v>0.256397012</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.273833465</v>
+        <v>0.273734655</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.142861903</v>
+        <v>0.142768189</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.122941162</v>
+        <v>0.122850164</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.144858468</v>
+        <v>0.144933332</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.163268472</v>
+        <v>0.163347304</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.213552144</v>
+        <v>0.213638907</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.088340238</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08834017800000001</v>
+        <v>0.08834038</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088339368</v>
+        <v>0.088339376</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.088340768</v>
+        <v>0.088340723</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088339599</v>
+        <v>0.08834036100000001</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.08833983300000001</v>
+        <v>0.08834085</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088339528</v>
+        <v>0.088340394</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.08834075600000001</v>
+        <v>0.088340183</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.004439655</v>
+        <v>0.004643084</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.015072242</v>
+        <v>-0.01466024</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.002242063</v>
+        <v>-0.001769952</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>-0.006601081</v>
+        <v>0.000608822</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.0016624</v>
+        <v>-0.004502588</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.00051342</v>
+        <v>-0.001163992</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.010876311</v>
+        <v>-0.003880733</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.005872552</v>
+        <v>-0.005462242</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.004978206</v>
+        <v>0.005479496</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.000980425</v>
+        <v>-0.006088842</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004439655</v>
+        <v>0.004643084</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.015072242</v>
+        <v>-0.01466024</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.002242063</v>
+        <v>-0.001769952</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.006601081</v>
+        <v>0.000608822</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.0016624</v>
+        <v>-0.004502588</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.00051342</v>
+        <v>-0.001163992</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.010876311</v>
+        <v>-0.003880733</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.005872552</v>
+        <v>-0.005462242</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.004978206</v>
+        <v>0.005479496</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.000980425</v>
+        <v>-0.006088842</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8773,26 +8773,26 @@
         <v>0.09303839</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.092807241</v>
+        <v>0.092801779</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.082658756</v>
+        <v>0.082651671</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.094478083</v>
+        <v>0.09447224799999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.07535291</v>
+        <v>0.07534785400000001</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.077631723</v>
+        <v>0.077631437</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.07116739499999999</v>
+        <v>0.071168949</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.08520251</v>
+        <v>0.085204247</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8901,26 +8901,26 @@
         <v>0.08468653499999999</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.08512908900000001</v>
+        <v>0.08512407900000001</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.076354452</v>
+        <v>0.07634787899999999</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.087783493</v>
+        <v>0.087777999</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.07044241900000001</v>
+        <v>0.070439587</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.072907687</v>
+        <v>0.072907188</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.06713100900000001</v>
+        <v>0.067132276</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.080675703</v>
+        <v>0.080675522</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9583,11 +9583,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>45550</v>
+        <v>41350</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 48,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 47,450원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2200021822429607</v>
+        <v>0.2200011553446457</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577676058516068</v>
+        <v>0.04577692183975356</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03769588162953518</v>
+        <v>0.03769753395207513</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05040849687653878</v>
+        <v>0.05042675028256319</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.15</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.85</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 137532억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 138532억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 143236억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146410억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 149981억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154149억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 148139억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152377억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 154428억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 157070억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163996억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163427억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 174480억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 171603억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 179788억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 175463억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 137532억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 138532억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 143236억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146410억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 149981억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154149억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 148139억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152377억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 154428억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 157070억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163996억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163427억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 174480억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 171603억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 179788억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 175463억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2142,43 +2142,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3992억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3994억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4332억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4341억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4662억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4680억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5072억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5100억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5429억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5463억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5825억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5858억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6216억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6243억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2202,43 +2202,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3992억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3994억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4332억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4341억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4662억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4680억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5072억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5100억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5429억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5463억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5825억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5858억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6216억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6243억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.77% / 부채 5.04% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
+          <t>· 이자율 자산 3.77% / 부채 5.05% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.7, "op_wape_pct": 44.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 13.3, "wape_trend": 12.7, "adopted": true, "decision": "adopted"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 3305.76, "rev_act": 2973.45, "op_pred": 199.62, "op_act": 266.31}, {"q": "2025Q4", "rev_pred": 4386.85, "rev_act": 3678.3, "op_pred": 264.9, "op_act": 473.48}, {"q": "2026Q1", "rev_pred": 3679.41, "rev_act": 3452.39, "op_pred": 222.19, "op_act": 513.79}, {"q": "2026Q2", "rev_pred": 3680.92, "rev_act": 3622.2, "op_pred": 222.28, "op_act": 379.11}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.7, "op_wape_pct": 44.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": 12.7, "adopted": "undetermined", "decision": "undetermined", "note": "현재 채택 조합(suppliers_mentions·시차 2·ma4·창 12)을 동결 데이터로 재적합할 수 없음(짝·고객 모델 부족) → 연동 WAPE 없음, undetermined(유의성 조건만으로 채택)"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 3305.76, "rev_act": 2973.45, "op_pred": 199.62, "op_act": 266.31}, {"q": "2025Q4", "rev_pred": 4386.85, "rev_act": 3678.3, "op_pred": 264.9, "op_act": 473.48}, {"q": "2026Q1", "rev_pred": 3679.41, "rev_act": 3452.39, "op_pred": 222.19, "op_act": 513.79}, {"q": "2026Q2", "rev_pred": 3680.92, "rev_act": 3622.2, "op_pred": 222.28, "op_act": 379.11}]}</t>
         </is>
       </c>
     </row>
@@ -6705,29 +6705,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.209566393</v>
+        <v>0.218351601</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.256397012</v>
+        <v>0.284233693</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.273734655</v>
+        <v>0.30913466</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.142768189</v>
+        <v>0.175459824</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.122850164</v>
+        <v>0.133822925</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.144933332</v>
+        <v>0.116231526</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.163347304</v>
+        <v>0.113224469</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.213638907</v>
+        <v>0.151501408</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7019,32 +7019,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.088340238</v>
+        <v>0.08834039</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08834038</v>
+        <v>0.088340947</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088339376</v>
+        <v>0.088339238</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.088340723</v>
+        <v>0.08833935399999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08834036100000001</v>
+        <v>0.08833914900000001</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.08834085</v>
+        <v>0.088340141</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088340394</v>
+        <v>0.088339927</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088340183</v>
+        <v>0.088340642</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.004643084</v>
+        <v>0.005357598</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.01466024</v>
+        <v>-0.013514227</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.001769952</v>
+        <v>0.000113072</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.000608822</v>
+        <v>-0.002349125</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.004502588</v>
+        <v>-0.002919139</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.001163992</v>
+        <v>0.001110012</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.003880733</v>
+        <v>-0.009114636000000001</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.005462242</v>
+        <v>0.001491572</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.005479496</v>
+        <v>-0.001806148</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.006088842</v>
+        <v>0.00482999</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004643084</v>
+        <v>0.005357598</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.01466024</v>
+        <v>-0.013514227</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.001769952</v>
+        <v>0.000113072</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000608822</v>
+        <v>-0.002349125</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.004502588</v>
+        <v>-0.002919139</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.001163992</v>
+        <v>0.001110012</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.003880733</v>
+        <v>-0.009114636000000001</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.005462242</v>
+        <v>0.001491572</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.005479496</v>
+        <v>-0.001806148</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.006088842</v>
+        <v>0.00482999</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8770,29 +8770,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.09303839</v>
+        <v>0.093662308</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.092801779</v>
+        <v>0.094648633</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.082651671</v>
+        <v>0.084577214</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.09447224799999999</v>
+        <v>0.096606951</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.07534785400000001</v>
+        <v>0.07610170099999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.077631437</v>
+        <v>0.076921278</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.071168949</v>
+        <v>0.069737275</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.085204247</v>
+        <v>0.082972401</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8898,29 +8898,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.08468653499999999</v>
+        <v>0.085254445</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.08512407900000001</v>
+        <v>0.086822187</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07634787899999999</v>
+        <v>0.078137707</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.087777999</v>
+        <v>0.08978939499999999</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.070439587</v>
+        <v>0.07117003</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.072907188</v>
+        <v>0.072269683</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.067132276</v>
+        <v>0.065804344</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.080675522</v>
+        <v>0.078581966</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2200011553446457</v>
+        <v>0.22</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577692183975356</v>
+        <v>0.04577696323903657</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03769753395207513</v>
+        <v>0.03770332813094393</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05042675028256319</v>
+        <v>0.05047767680165551</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40661,7 +40661,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1510.6</v>
+        <v>1521.4</v>
       </c>
     </row>
     <row r="30">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.37</v>
+        <v>27.18</v>
       </c>
     </row>
     <row r="32">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.194</v>
+        <v>0.1953</v>
       </c>
     </row>
     <row r="34">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="35">
@@ -40721,7 +40721,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16800</v>
+        <v>16900</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146410억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146407억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 154149억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154177억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152377억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152436억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 157070억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 157160억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163427억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163550억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 171603억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 171723억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 175463억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 175578억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146410억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146407억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 154149억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154177억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152377억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152436억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 157070억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 157160억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163427억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163550억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 171603억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 171723억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 175463억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 175578억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2178,7 +2178,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6243억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6244억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2238,7 +2238,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6243억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6244억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4583,7 +4583,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.77% / 부채 5.05% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
+          <t>· 이자율 자산 3.77% / 부채 5.04% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>41350</v>
+        <v>41150</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>46380</v>
+        <v>46340</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6708,26 +6708,26 @@
         <v>0.218351601</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.284233693</v>
+        <v>0.284206086</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.30913466</v>
+        <v>0.309372966</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175459824</v>
+        <v>0.175911734</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.133822925</v>
+        <v>0.134467207</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.116231526</v>
+        <v>0.117093934</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.113224469</v>
+        <v>0.11379869</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.151501408</v>
+        <v>0.151815094</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.08834039</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.088340947</v>
+        <v>0.088340696</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088339238</v>
+        <v>0.088340917</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08833935399999999</v>
+        <v>0.088340825</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08833914900000001</v>
+        <v>0.088339274</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.088340141</v>
+        <v>0.08833927</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088339927</v>
+        <v>0.088340089</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088340642</v>
+        <v>0.088339532</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.005357598</v>
+        <v>0.00624404</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.013514227</v>
+        <v>-0.012586881</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.000113072</v>
+        <v>0.000688774</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>-0.002349125</v>
+        <v>0.000273691</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.002919139</v>
+        <v>-0.000439672</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.001110012</v>
+        <v>0.007575223</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.009114636000000001</v>
+        <v>-0.010798918</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>0.001491572</v>
+        <v>-0.0009825669999999999</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.001806148</v>
+        <v>0.003993053</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.00482999</v>
+        <v>-0.000769859</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.005357598</v>
+        <v>0.00624404</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.013514227</v>
+        <v>-0.012586881</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000113072</v>
+        <v>0.000688774</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.002349125</v>
+        <v>0.000273691</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.002919139</v>
+        <v>-0.000439672</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.001110012</v>
+        <v>0.007575223</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.009114636000000001</v>
+        <v>-0.010798918</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.001491572</v>
+        <v>-0.0009825669999999999</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.001806148</v>
+        <v>0.003993053</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.00482999</v>
+        <v>-0.000769859</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8776,23 +8776,23 @@
         <v>0.094648633</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.084577214</v>
+        <v>0.08458718799999999</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.096606951</v>
+        <v>0.096642848</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.07610170099999999</v>
+        <v>0.076136247</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.076921278</v>
+        <v>0.076970133</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.069737275</v>
+        <v>0.069772364</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.082972401</v>
+        <v>0.083010503</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8901,26 +8901,26 @@
         <v>0.085254445</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.086822187</v>
+        <v>0.08681968299999999</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.078137707</v>
+        <v>0.07815171</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.08978939499999999</v>
+        <v>0.089820487</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.07117003</v>
+        <v>0.07120449199999999</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.072269683</v>
+        <v>0.072313944</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.065804344</v>
+        <v>0.065839603</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.078581966</v>
+        <v>0.07861855800000001</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9583,11 +9583,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>41350</v>
+        <v>41150</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 47,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,300원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.22</v>
+        <v>0.2199981264796553</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577696323903657</v>
+        <v>0.0457769515828674</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03770332813094393</v>
+        <v>0.0376995526370137</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05047767680165551</v>
+        <v>0.05043656439420031</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.18</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.31</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146407억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146403억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 154177억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154161억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152436억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152407억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 157160억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 157118억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163550억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163499억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 171723억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 171674억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 175578억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 175531억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146407억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146403억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 154177억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154161억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152436억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152407억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 157160억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 157118억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163550억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163499억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 171723억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 171674억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 175578억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 175531억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6708,26 +6708,26 @@
         <v>0.218351601</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.284206086</v>
+        <v>0.284170196</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.309372966</v>
+        <v>0.309227657</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175911734</v>
+        <v>0.175684738</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.134467207</v>
+        <v>0.134165274</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.117093934</v>
+        <v>0.116781181</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.11379869</v>
+        <v>0.113602664</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.151815094</v>
+        <v>0.151727497</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.08834039</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.088340696</v>
+        <v>0.08834101499999999</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088340917</v>
+        <v>0.08833962300000001</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.088340825</v>
+        <v>0.088340168</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088339274</v>
+        <v>0.088339734</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.08833927</v>
+        <v>0.088339529</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088340089</v>
+        <v>0.088339533</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088339532</v>
+        <v>0.088340239</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.00624404</v>
+        <v>0.00588989</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.012586881</v>
+        <v>-0.013322216</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.000688774</v>
+        <v>-2.3113e-05</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.000273691</v>
+        <v>0.00156569</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.000439672</v>
+        <v>-0.000495483</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.007575223</v>
+        <v>-0.00205929</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.010798918</v>
+        <v>-0.008753986</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.0009825669999999999</v>
+        <v>-0.003206306</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.003993053</v>
+        <v>-0.001323009</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000769859</v>
+        <v>-0.002868483</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.00624404</v>
+        <v>0.00588989</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.012586881</v>
+        <v>-0.013322216</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000688774</v>
+        <v>-2.3113e-05</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000273691</v>
+        <v>0.00156569</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.000439672</v>
+        <v>-0.000495483</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.007575223</v>
+        <v>-0.00205929</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.010798918</v>
+        <v>-0.008753986</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.0009825669999999999</v>
+        <v>-0.003206306</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.003993053</v>
+        <v>-0.001323009</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000769859</v>
+        <v>-0.002868483</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8773,26 +8773,26 @@
         <v>0.093662308</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.094648633</v>
+        <v>0.094645904</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.08458718799999999</v>
+        <v>0.084579918</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.096642848</v>
+        <v>0.096625344</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.076136247</v>
+        <v>0.07612139</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.076970133</v>
+        <v>0.076949753</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.069772364</v>
+        <v>0.069758313</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.083010503</v>
+        <v>0.082996105</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8901,26 +8901,26 @@
         <v>0.085254445</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.08681968299999999</v>
+        <v>0.08681717899999999</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07815171</v>
+        <v>0.078144978</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.089820487</v>
+        <v>0.08980415999999999</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.07120449199999999</v>
+        <v>0.071188521</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.072313944</v>
+        <v>0.07229658899999999</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.065839603</v>
+        <v>0.06582613</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.07861855800000001</v>
+        <v>0.07860302600000001</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2199981264796553</v>
+        <v>0.220000638793957</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0457769515828674</v>
+        <v>0.04577666728429147</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.0376995526370137</v>
+        <v>0.03769809096643739</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05043656439420031</v>
+        <v>0.05041467869059332</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>41150</v>
+        <v>38950</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6455,7 +6455,7 @@
         <v>35800</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>41000</v>
+        <v>38700</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>46340</v>
+        <v>45108.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>41150</v>
+        <v>38950</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.05</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146403억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146392억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 154161억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154096억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152407억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152288억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 157118억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 156945억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163499억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163284억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 171674억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 171464억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 175531억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 175328억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146403억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146392억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 154161억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154096억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152407억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152288억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 157118억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 156945억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163499억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163284억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 171674억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 171464억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 175531억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 175328억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2166,19 +2166,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5463억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5462억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5858억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5857억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6244억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6242억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2226,19 +2226,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5463억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5462억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5858억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5857억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6244억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6242억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.77% / 부채 5.04% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
+          <t>· 이자율 자산 3.77% / 부채 5.05% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>38950</v>
+        <v>37400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6455,7 +6455,7 @@
         <v>35800</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>38700</v>
+        <v>34500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>45108.3</v>
+        <v>43971.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6708,26 +6708,26 @@
         <v>0.218351601</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.284170196</v>
+        <v>0.284081852</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.309227657</v>
+        <v>0.308678392</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175684738</v>
+        <v>0.174768422</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.134165274</v>
+        <v>0.13292188</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.116781181</v>
+        <v>0.115387427</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.113602664</v>
+        <v>0.112708772</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.151727497</v>
+        <v>0.151296301</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.08834039</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08834101499999999</v>
+        <v>0.088340643</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.08833962300000001</v>
+        <v>0.088338948</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.088340168</v>
+        <v>0.08833993699999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088339734</v>
+        <v>0.088340157</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.088339529</v>
+        <v>0.088340346</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088339533</v>
+        <v>0.088339836</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088340239</v>
+        <v>0.088340632</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.00588989</v>
+        <v>0.00530175</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.013322216</v>
+        <v>-0.013456659</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-2.3113e-05</v>
+        <v>-9.101e-05</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.00156569</v>
+        <v>-0.001622087</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.000495483</v>
+        <v>-0.002867333</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.00205929</v>
+        <v>-0.006608591</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.008753986</v>
+        <v>-6.7464e-05</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.003206306</v>
+        <v>0.003934382</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.001323009</v>
+        <v>-0.00065193</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.002868483</v>
+        <v>0.001525968</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.00588989</v>
+        <v>0.00530175</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.013322216</v>
+        <v>-0.013456659</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-2.3113e-05</v>
+        <v>-9.101e-05</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.00156569</v>
+        <v>-0.001622087</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.000495483</v>
+        <v>-0.002867333</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.00205929</v>
+        <v>-0.006608591</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.008753986</v>
+        <v>-6.7464e-05</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.003206306</v>
+        <v>0.003934382</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.001323009</v>
+        <v>-0.00065193</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.002868483</v>
+        <v>0.001525968</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8773,26 +8773,26 @@
         <v>0.093662308</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.094645904</v>
+        <v>0.094640444</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.084579918</v>
+        <v>0.084547923</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.096625344</v>
+        <v>0.096557401</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.07612139</v>
+        <v>0.076051152</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.076949753</v>
+        <v>0.076870616</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.069758313</v>
+        <v>0.069696915</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.082996105</v>
+        <v>0.082930741</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8901,26 +8901,26 @@
         <v>0.085254445</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.08681717899999999</v>
+        <v>0.08681217200000001</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.078144978</v>
+        <v>0.078113085</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.08980415999999999</v>
+        <v>0.08974312399999999</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071188521</v>
+        <v>0.071124349</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.07229658899999999</v>
+        <v>0.07222139800000001</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.06582613</v>
+        <v>0.065765503</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.07860302600000001</v>
+        <v>0.078541505</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9583,11 +9583,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>38950</v>
+        <v>37400</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 41,050원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.220000638793957</v>
+        <v>0.2199980824340304</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577666728429147</v>
+        <v>0.04577705831166107</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03769809096643739</v>
+        <v>0.03770089459587493</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05041467869059332</v>
+        <v>0.05046515597315091</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25.6</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146392억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146391억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 154096억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154149억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152288억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152394억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 156945억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 157105억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163284억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163499억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 171464억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 171673억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 175328억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 175530억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146392억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146391억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 154096억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154149억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152288억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152394억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 156945억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 157105억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163284억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163499억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 171464억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 171673억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 175328억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 175530억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2166,19 +2166,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5462억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5463억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5857억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5858억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6242억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6244억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2226,19 +2226,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5462억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5463억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5857억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5858억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6242억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6244억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.77% / 부채 5.05% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
+          <t>· 이자율 자산 3.77% / 부채 5.04% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0377, 0.0504] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>37400</v>
+        <v>39850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43971.4</v>
+        <v>43481.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6708,26 +6708,26 @@
         <v>0.218351601</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.284081852</v>
+        <v>0.284068048</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.308678392</v>
+        <v>0.309125942</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.174768422</v>
+        <v>0.175591023</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.13292188</v>
+        <v>0.134077309</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.115387427</v>
+        <v>0.116865721</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.112708772</v>
+        <v>0.113686968</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.151296301</v>
+        <v>0.151815766</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.08834039</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.088340643</v>
+        <v>0.088339443</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088338948</v>
+        <v>0.088339827</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08833993699999999</v>
+        <v>0.08834012400000001</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088340157</v>
+        <v>0.088340297</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.088340346</v>
+        <v>0.088339869</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088339836</v>
+        <v>0.088339709</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088340632</v>
+        <v>0.088340511</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.00530175</v>
+        <v>0.00557025</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.013456659</v>
+        <v>-0.013392571</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-9.101e-05</v>
+        <v>-7.561100000000001e-05</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>-0.001622087</v>
+        <v>0.000459264</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.002867333</v>
+        <v>-0.003874881</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.006608591</v>
+        <v>-0.003218024</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-6.7464e-05</v>
+        <v>-0.002332267</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>0.003934382</v>
+        <v>-0.003450427</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.00065193</v>
+        <v>-0.001482273</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.001525968</v>
+        <v>-0.002798997</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.00530175</v>
+        <v>0.00557025</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.013456659</v>
+        <v>-0.013392571</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-9.101e-05</v>
+        <v>-7.561100000000001e-05</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.001622087</v>
+        <v>0.000459264</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.002867333</v>
+        <v>-0.003874881</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.006608591</v>
+        <v>-0.003218024</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-6.7464e-05</v>
+        <v>-0.002332267</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.003934382</v>
+        <v>-0.003450427</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.00065193</v>
+        <v>-0.001482273</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.001525968</v>
+        <v>-0.002798997</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8773,26 +8773,26 @@
         <v>0.093662308</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.094640444</v>
+        <v>0.094637715</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.084547923</v>
+        <v>0.08457556400000001</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.096557401</v>
+        <v>0.09661955699999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.076051152</v>
+        <v>0.076116377</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.076870616</v>
+        <v>0.076951402</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.069696915</v>
+        <v>0.06975970099999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.082930741</v>
+        <v>0.08299595799999999</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8904,23 +8904,23 @@
         <v>0.08681217200000001</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.078113085</v>
+        <v>0.078138427</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.08974312399999999</v>
+        <v>0.089798709</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071124349</v>
+        <v>0.071183755</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.07222139800000001</v>
+        <v>0.07229804400000001</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.065765503</v>
+        <v>0.06582565899999999</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.078541505</v>
+        <v>0.07860613800000001</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9583,11 +9583,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>37400</v>
+        <v>39850</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 41,050원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 38,900원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2199980824340304</v>
+        <v>0.2199991482475193</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577705831166107</v>
+        <v>0.04577672442980701</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03770089459587493</v>
+        <v>0.03769942073573988</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05046515597315091</v>
+        <v>0.05044076622741655</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.58</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.8</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146391억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146382억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 154149억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 154079억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152394억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152265억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 157105억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 156916억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163499억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163259억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 171673억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 171440억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 175530억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 175305억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146391억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146382억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 154149억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 154079억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152394억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152265억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 157105억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 156916억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163499억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163259억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 171673억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 171440억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 175530억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 175305억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2166,19 +2166,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5463억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5462억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5858억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5857억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6244억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6242억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2226,19 +2226,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5463억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5462억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5858억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5857억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6244억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6242억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>39850</v>
+        <v>37450</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43481.2</v>
+        <v>41768.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6708,26 +6708,26 @@
         <v>0.218351601</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.284068048</v>
+        <v>0.283990747</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.309125942</v>
+        <v>0.30853599</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175591023</v>
+        <v>0.174591407</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.134077309</v>
+        <v>0.132712667</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.116865721</v>
+        <v>0.115296708</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.113686968</v>
+        <v>0.112672178</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.151815766</v>
+        <v>0.151317329</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.08834039</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.088339443</v>
+        <v>0.088340461</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088339827</v>
+        <v>0.088339678</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08834012400000001</v>
+        <v>0.088340839</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088340297</v>
+        <v>0.088339682</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.088339869</v>
+        <v>0.08834030599999999</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088339709</v>
+        <v>0.088340379</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088340511</v>
+        <v>0.088340012</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.00557025</v>
+        <v>0.004644012</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.013392571</v>
+        <v>-0.014747196</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-7.561100000000001e-05</v>
+        <v>-0.001369235</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.000459264</v>
+        <v>0.003362697</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.003874881</v>
+        <v>-0.005974296</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.003218024</v>
+        <v>-0.003937885</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.002332267</v>
+        <v>-0.005564695</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.003450427</v>
+        <v>-0.004630646</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.001482273</v>
+        <v>-0.002022593</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.002798997</v>
+        <v>-0.00656104</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.00557025</v>
+        <v>0.004644012</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.013392571</v>
+        <v>-0.014747196</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-7.561100000000001e-05</v>
+        <v>-0.001369235</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000459264</v>
+        <v>0.003362697</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.003874881</v>
+        <v>-0.005974296</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.003218024</v>
+        <v>-0.003937885</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.002332267</v>
+        <v>-0.005564695</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.003450427</v>
+        <v>-0.004630646</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.001482273</v>
+        <v>-0.002022593</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.002798997</v>
+        <v>-0.00656104</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8773,26 +8773,26 @@
         <v>0.093662308</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.094637715</v>
+        <v>0.094632256</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.08457556400000001</v>
+        <v>0.08454107499999999</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.09661955699999999</v>
+        <v>0.09654723699999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.076116377</v>
+        <v>0.07604032600000001</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.076951402</v>
+        <v>0.07686147</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.06975970099999999</v>
+        <v>0.069690768</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.08299595799999999</v>
+        <v>0.082922827</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8901,26 +8901,26 @@
         <v>0.085254445</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.08681217200000001</v>
+        <v>0.08680716400000001</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.078138427</v>
+        <v>0.07810653300000001</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.089798709</v>
+        <v>0.08973126100000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071183755</v>
+        <v>0.071112157</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.07229804400000001</v>
+        <v>0.072212794</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.06582565899999999</v>
+        <v>0.06575966</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.07860613800000001</v>
+        <v>0.078535541</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9583,11 +9583,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>39850</v>
+        <v>37450</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 38,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 36,550원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2199991482475193</v>
+        <v>0.2200021308331557</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577672442980701</v>
+        <v>0.04577695081940956</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03769942073573988</v>
+        <v>0.03769816837445625</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05044076622741655</v>
+        <v>0.05042769546481791</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.19</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.12</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/082740_model.xlsx
+++ b/argus/kship/models/082740_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 146382억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 146351억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 154079억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 153998억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 152265억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 152135억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 156916억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 156738억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 163259억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 163065억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 171440억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 171250억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 175305억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 175122억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 146382억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 146351억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 154079억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 153998억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 152265억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 152135억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 156916억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 156738억 × 비례계수 0.1284 × 계절비중 Q1 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 163259억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 163065억 × 비례계수 0.1284 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 171440억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 171250억 × 비례계수 0.1284 × 계절비중 Q3 0.228(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 175305억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 175122억 × 비례계수 0.1284 × 계절비중 Q4 0.288(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2154,31 +2154,31 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4680억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4679억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5100억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5099억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5462억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5461억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5857억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 5855억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6242억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 +716.13억이 이자손익 추정 +24.97억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 6240억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2214,31 +2214,31 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4680억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4679억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5100억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5099억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5462억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5461억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5857억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5855억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6242억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6240억 × 3.77%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 316억 × 5.04%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4434,7 +4434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5424,35 +5424,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5543,35 +5543,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5662,35 +5662,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5781,35 +5781,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5900,35 +5900,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6019,35 +6019,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6138,35 +6138,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6273,7 +6273,7 @@
         <v>49350</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>37450</v>
+        <v>30850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6455,7 +6455,7 @@
         <v>35800</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>34500</v>
+        <v>30750</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6546,7 +6546,7 @@
         <v>46760.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>41768.2</v>
+        <v>39062.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6708,26 +6708,26 @@
         <v>0.218351601</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.283990747</v>
+        <v>0.283717432</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.30853599</v>
+        <v>0.307850135</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.174591407</v>
+        <v>0.17359179</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.132712667</v>
+        <v>0.131426479</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.115296708</v>
+        <v>0.114205098</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.112672178</v>
+        <v>0.112022416</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.151317329</v>
+        <v>0.15109309</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7022,29 +7022,29 @@
         <v>0.08834039</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.088340461</v>
+        <v>0.08833991400000001</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.088339678</v>
+        <v>0.08833934</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.088340839</v>
+        <v>0.08833978100000001</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.088339682</v>
+        <v>0.088339245</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.08834030599999999</v>
+        <v>0.088339523</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.088340379</v>
+        <v>0.08834043699999999</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.088340012</v>
+        <v>0.088339985</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8379,36 +8379,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.004644012</v>
+        <v>0.004327025</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.014747196</v>
+        <v>-0.015144115</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.001369235</v>
+        <v>-0.001606443</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.003362697</v>
+        <v>-0.007039094</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.005974296</v>
+        <v>-0.000382557</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.003937885</v>
+        <v>-0.011151614</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.005564695</v>
+        <v>-0.004068586</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.004630646</v>
+        <v>-0.000404876</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.002022593</v>
+        <v>-0.004032331</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.00656104</v>
+        <v>-0.007299927</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8507,36 +8507,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004644012</v>
+        <v>0.004327025</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.014747196</v>
+        <v>-0.015144115</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.001369235</v>
+        <v>-0.001606443</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.003362697</v>
+        <v>-0.007039094</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.005974296</v>
+        <v>-0.000382557</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.003937885</v>
+        <v>-0.011151614</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.005564695</v>
+        <v>-0.004068586</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.004630646</v>
+        <v>-0.000404876</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.002022593</v>
+        <v>-0.004032331</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.00656104</v>
+        <v>-0.007299927</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8773,26 +8773,26 @@
         <v>0.093662308</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.094632256</v>
+        <v>0.09461314799999999</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.08454107499999999</v>
+        <v>0.084502652</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.09654723699999999</v>
+        <v>0.096474164</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.07604032600000001</v>
+        <v>0.07597182399999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.07686147</v>
+        <v>0.07678979700000001</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.069690768</v>
+        <v>0.069637586</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.082922827</v>
+        <v>0.082868132</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8901,26 +8901,26 @@
         <v>0.085254445</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.08680716400000001</v>
+        <v>0.086789637</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07810653300000001</v>
+        <v>0.078070931</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.08973126100000001</v>
+        <v>0.089663013</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071112157</v>
+        <v>0.071047543</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.072212794</v>
+        <v>0.072146487</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.06575966</v>
+        <v>0.06570844000000001</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.078535541</v>
+        <v>0.078479167</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9583,11 +9583,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>37450</v>
+        <v>30850</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 36,550원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 33,800원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2200021308331557</v>
+        <v>0.2200033687909239</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04577695081940956</v>
+        <v>0.04577712598521467</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03769816837445625</v>
+        <v>0.03769960534880049</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05042769546481791</v>
+        <v>0.05044020807362085</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40661,7 +40661,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1521.4</v>
+        <v>1521.3</v>
       </c>
     </row>
     <row r="30">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.62</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="32">
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.81</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="33">
